--- a/Documents/DBdesign.xlsx
+++ b/Documents/DBdesign.xlsx
@@ -1,36 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitLab\joboffer\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82E01B8D-64A9-47F1-86BA-ABA48CF1A353}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CF10D9F-43C9-40F4-8D65-AD815682AEAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{BEC21941-B947-480A-A7E6-7B63159DE119}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" activeTab="2" xr2:uid="{BEC21941-B947-480A-A7E6-7B63159DE119}"/>
   </bookViews>
   <sheets>
     <sheet name="RBAC+ABAC" sheetId="1" r:id="rId1"/>
-    <sheet name="Candidate" sheetId="2" r:id="rId2"/>
+    <sheet name="MSForms" sheetId="2" r:id="rId2"/>
+    <sheet name="Company Setup" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="2"/>
@@ -40,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="92">
   <si>
     <t>JobOfferUsers</t>
   </si>
@@ -243,24 +233,9 @@
     <t>CandidateApplications</t>
   </si>
   <si>
-    <t>HiringCompanyId</t>
-  </si>
-  <si>
-    <t>ApplicationStatusId</t>
-  </si>
-  <si>
     <t>CurrentWorkflowStatusId</t>
   </si>
   <si>
-    <t>ApplicationDate</t>
-  </si>
-  <si>
-    <t>EndorsementDate</t>
-  </si>
-  <si>
-    <t>TAOwnerId</t>
-  </si>
-  <si>
     <t>RequestSentDate</t>
   </si>
   <si>
@@ -286,6 +261,51 @@
   </si>
   <si>
     <t>ReferenceNumber</t>
+  </si>
+  <si>
+    <t>FileName</t>
+  </si>
+  <si>
+    <t>FilePath</t>
+  </si>
+  <si>
+    <t>FileSize</t>
+  </si>
+  <si>
+    <t>FileTypeId</t>
+  </si>
+  <si>
+    <t>UploadedBy</t>
+  </si>
+  <si>
+    <t>UploadedDate</t>
+  </si>
+  <si>
+    <t>FileTypes</t>
+  </si>
+  <si>
+    <t>TypeName</t>
+  </si>
+  <si>
+    <t>SubmittedDocuments</t>
+  </si>
+  <si>
+    <t>CurrencyId</t>
+  </si>
+  <si>
+    <t>Currencies</t>
+  </si>
+  <si>
+    <t>Currency</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>CreatedBy</t>
+  </si>
+  <si>
+    <t>CreatedAt</t>
   </si>
 </sst>
 </file>
@@ -991,15 +1011,15 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{026B99F0-FC57-47AB-AF03-F4ABCCD02BF2}">
-  <dimension ref="B2:F16"/>
+  <dimension ref="B2:H16"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="22.54296875" customWidth="1"/>
-    <col min="4" max="4" width="23.6328125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20.26953125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="24.453125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B2" s="1" t="s">
         <v>53</v>
       </c>
@@ -1007,10 +1027,13 @@
         <v>65</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="3" spans="2:6" x14ac:dyDescent="0.35">
+        <v>85</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="3" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B3" t="s">
         <v>1</v>
       </c>
@@ -1020,8 +1043,11 @@
       <c r="F3" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="H3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B4" t="s">
         <v>54</v>
       </c>
@@ -1031,110 +1057,179 @@
       <c r="F4" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="5" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="H4" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="5" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B5" t="s">
         <v>55</v>
       </c>
       <c r="D5" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="F5" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="6" spans="2:6" x14ac:dyDescent="0.35">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="6" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B6" t="s">
         <v>56</v>
       </c>
       <c r="D6" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="F6" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="7" spans="2:6" x14ac:dyDescent="0.35">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="7" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B7" t="s">
         <v>3</v>
       </c>
       <c r="D7" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="F7" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="8" spans="2:6" x14ac:dyDescent="0.35">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="8" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B8" t="s">
         <v>57</v>
       </c>
       <c r="D8" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="F8" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="9" spans="2:6" x14ac:dyDescent="0.35">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="9" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B9" t="s">
         <v>58</v>
       </c>
       <c r="D9" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="F9" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="10" spans="2:6" x14ac:dyDescent="0.35">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="10" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B10" t="s">
         <v>59</v>
       </c>
       <c r="D10" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="F10" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="11" spans="2:6" x14ac:dyDescent="0.35">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="11" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B11" t="s">
         <v>60</v>
       </c>
       <c r="D11" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="F11" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="12" spans="2:6" x14ac:dyDescent="0.35">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="12" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B12" t="s">
         <v>61</v>
       </c>
       <c r="D12" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="13" spans="2:6" x14ac:dyDescent="0.35">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="13" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B13" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="14" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B14" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="15" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B15" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="16" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B16" t="s">
         <v>64</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9AD6FEA5-0945-4178-A2F8-A72772503D4A}">
+  <dimension ref="B2:D9"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" width="21.36328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.1796875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B2" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="5" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B5" t="s">
+        <v>75</v>
+      </c>
+      <c r="D5" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="6" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="7" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B7" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="8" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B8" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="9" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B9" t="s">
+        <v>91</v>
       </c>
     </row>
   </sheetData>

--- a/Documents/DBdesign.xlsx
+++ b/Documents/DBdesign.xlsx
@@ -1,21 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitLab\joboffer\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CF10D9F-43C9-40F4-8D65-AD815682AEAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37AA3DD0-F6FA-4B32-8883-DCF8FAB8608A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" activeTab="2" xr2:uid="{BEC21941-B947-480A-A7E6-7B63159DE119}"/>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{BEC21941-B947-480A-A7E6-7B63159DE119}"/>
   </bookViews>
   <sheets>
     <sheet name="RBAC+ABAC" sheetId="1" r:id="rId1"/>
     <sheet name="MSForms" sheetId="2" r:id="rId2"/>
     <sheet name="Company Setup" sheetId="3" r:id="rId3"/>
+    <sheet name="Analysis" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -30,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="113">
   <si>
     <t>JobOfferUsers</t>
   </si>
@@ -233,9 +234,6 @@
     <t>CandidateApplications</t>
   </si>
   <si>
-    <t>CurrentWorkflowStatusId</t>
-  </si>
-  <si>
     <t>RequestSentDate</t>
   </si>
   <si>
@@ -306,6 +304,72 @@
   </si>
   <si>
     <t>CreatedAt</t>
+  </si>
+  <si>
+    <t>SalaryMatrix</t>
+  </si>
+  <si>
+    <t>SalaryMatrixId</t>
+  </si>
+  <si>
+    <t>WorkFlowStatus</t>
+  </si>
+  <si>
+    <t>WorkFlowName</t>
+  </si>
+  <si>
+    <t>ShortName</t>
+  </si>
+  <si>
+    <t>MatrixName</t>
+  </si>
+  <si>
+    <t>MatrixCode</t>
+  </si>
+  <si>
+    <t>EffectiveFrom</t>
+  </si>
+  <si>
+    <t>EffectiveTo</t>
+  </si>
+  <si>
+    <t>ApprovalStatusId</t>
+  </si>
+  <si>
+    <t>ApprovedByUserId</t>
+  </si>
+  <si>
+    <t>ApprovedAt</t>
+  </si>
+  <si>
+    <t>ModifiedAt</t>
+  </si>
+  <si>
+    <t>ModifiedBy</t>
+  </si>
+  <si>
+    <t>JobOfferWorkFlow</t>
+  </si>
+  <si>
+    <t>CandidateApplicationId</t>
+  </si>
+  <si>
+    <t>WorkFlowStatusId</t>
+  </si>
+  <si>
+    <t>IsDone</t>
+  </si>
+  <si>
+    <t>HiringCompanyId</t>
+  </si>
+  <si>
+    <t>HiringDivisionId</t>
+  </si>
+  <si>
+    <t>JobOfferProposal</t>
+  </si>
+  <si>
+    <t>SalaryMatrixBandId</t>
   </si>
 </sst>
 </file>
@@ -1027,10 +1091,10 @@
         <v>65</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="3" spans="2:8" x14ac:dyDescent="0.35">
@@ -1058,7 +1122,7 @@
         <v>16</v>
       </c>
       <c r="H4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="5" spans="2:8" x14ac:dyDescent="0.35">
@@ -1066,10 +1130,10 @@
         <v>55</v>
       </c>
       <c r="D5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="6" spans="2:8" x14ac:dyDescent="0.35">
@@ -1077,10 +1141,10 @@
         <v>56</v>
       </c>
       <c r="D6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.35">
@@ -1088,10 +1152,10 @@
         <v>3</v>
       </c>
       <c r="D7" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.35">
@@ -1099,10 +1163,10 @@
         <v>57</v>
       </c>
       <c r="D8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F8" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="9" spans="2:8" x14ac:dyDescent="0.35">
@@ -1110,10 +1174,10 @@
         <v>58</v>
       </c>
       <c r="D9" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F9" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="10" spans="2:8" x14ac:dyDescent="0.35">
@@ -1121,10 +1185,10 @@
         <v>59</v>
       </c>
       <c r="D10" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F10" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="11" spans="2:8" x14ac:dyDescent="0.35">
@@ -1132,10 +1196,10 @@
         <v>60</v>
       </c>
       <c r="D11" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F11" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="12" spans="2:8" x14ac:dyDescent="0.35">
@@ -1143,7 +1207,7 @@
         <v>61</v>
       </c>
       <c r="D12" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="13" spans="2:8" x14ac:dyDescent="0.35">
@@ -1173,11 +1237,185 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9AD6FEA5-0945-4178-A2F8-A72772503D4A}">
-  <dimension ref="B2:D9"/>
+  <dimension ref="B2:J18"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="21.36328125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.6328125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="19.90625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B2" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="3" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F3" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" t="s">
+        <v>1</v>
+      </c>
+      <c r="J3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" t="s">
+        <v>87</v>
+      </c>
+      <c r="F4" t="s">
+        <v>94</v>
+      </c>
+      <c r="H4" t="s">
+        <v>8</v>
+      </c>
+      <c r="J4" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="5" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B5" t="s">
+        <v>74</v>
+      </c>
+      <c r="D5" t="s">
+        <v>88</v>
+      </c>
+      <c r="F5" t="s">
+        <v>95</v>
+      </c>
+      <c r="H5" t="s">
+        <v>52</v>
+      </c>
+      <c r="J5" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="6" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B6" t="s">
+        <v>109</v>
+      </c>
+      <c r="F6" t="s">
+        <v>50</v>
+      </c>
+      <c r="H6" t="s">
+        <v>96</v>
+      </c>
+      <c r="J6" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="7" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B7" t="s">
+        <v>110</v>
+      </c>
+      <c r="H7" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="8" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B8" t="s">
+        <v>92</v>
+      </c>
+      <c r="H8" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="9" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B9" t="s">
+        <v>75</v>
+      </c>
+      <c r="H9" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="10" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B10" t="s">
+        <v>89</v>
+      </c>
+      <c r="H10" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="11" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B11" t="s">
+        <v>90</v>
+      </c>
+      <c r="H11" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="12" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="H12" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="13" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="H13" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="14" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="H14" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="15" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="H15" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="16" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="H16" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="17" spans="8:8" x14ac:dyDescent="0.35">
+      <c r="H17" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="18" spans="8:8" x14ac:dyDescent="0.35">
+      <c r="H18" t="s">
+        <v>104</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D3A9745-558A-479E-B1B2-9C6EC5EEDA6F}">
+  <dimension ref="B2:D11"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" width="20.26953125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:4" x14ac:dyDescent="0.35">
@@ -1185,7 +1423,7 @@
         <v>66</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>87</v>
+        <v>111</v>
       </c>
     </row>
     <row r="3" spans="2:4" x14ac:dyDescent="0.35">
@@ -1201,35 +1439,45 @@
         <v>16</v>
       </c>
       <c r="D4" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
     </row>
     <row r="5" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D5" t="s">
-        <v>89</v>
+        <v>112</v>
       </c>
     </row>
     <row r="6" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B6" t="s">
-        <v>67</v>
+        <v>109</v>
       </c>
     </row>
     <row r="7" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B7" t="s">
-        <v>86</v>
+        <v>110</v>
       </c>
     </row>
     <row r="8" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B8" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="9" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B9" t="s">
-        <v>91</v>
+        <v>75</v>
+      </c>
+    </row>
+    <row r="10" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B10" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="11" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B11" t="s">
+        <v>90</v>
       </c>
     </row>
   </sheetData>

--- a/Documents/DBdesign.xlsx
+++ b/Documents/DBdesign.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitLab\joboffer\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37AA3DD0-F6FA-4B32-8883-DCF8FAB8608A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6119FD84-0438-42A1-A530-ED2B73DFFBE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{BEC21941-B947-480A-A7E6-7B63159DE119}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="120">
   <si>
     <t>JobOfferUsers</t>
   </si>
@@ -370,6 +370,27 @@
   </si>
   <si>
     <t>SalaryMatrixBandId</t>
+  </si>
+  <si>
+    <t>OptionNumber</t>
+  </si>
+  <si>
+    <t>CurrentSalary</t>
+  </si>
+  <si>
+    <t>SalaryMidpoint</t>
+  </si>
+  <si>
+    <t>CompaRatio</t>
+  </si>
+  <si>
+    <t>IncreasePercentage</t>
+  </si>
+  <si>
+    <t>Justification</t>
+  </si>
+  <si>
+    <t>AnnualSalary</t>
   </si>
 </sst>
 </file>
@@ -1411,7 +1432,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D3A9745-558A-479E-B1B2-9C6EC5EEDA6F}">
-  <dimension ref="B2:D11"/>
+  <dimension ref="B2:D15"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="20.26953125" bestFit="1" customWidth="1"/>
@@ -1454,29 +1475,67 @@
       <c r="B6" t="s">
         <v>109</v>
       </c>
+      <c r="D6" t="s">
+        <v>113</v>
+      </c>
     </row>
     <row r="7" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B7" t="s">
         <v>110</v>
       </c>
+      <c r="D7" t="s">
+        <v>114</v>
+      </c>
     </row>
     <row r="8" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B8" t="s">
         <v>92</v>
       </c>
+      <c r="D8" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="9" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B9" t="s">
         <v>75</v>
       </c>
+      <c r="D9" t="s">
+        <v>115</v>
+      </c>
     </row>
     <row r="10" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B10" t="s">
         <v>89</v>
       </c>
+      <c r="D10" t="s">
+        <v>116</v>
+      </c>
     </row>
     <row r="11" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B11" t="s">
+        <v>90</v>
+      </c>
+      <c r="D11" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="12" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="D12" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="13" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="D13" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="14" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="D14" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="15" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="D15" t="s">
         <v>90</v>
       </c>
     </row>

--- a/Documents/DBdesign.xlsx
+++ b/Documents/DBdesign.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitLab\joboffer\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6119FD84-0438-42A1-A530-ED2B73DFFBE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B20B1CAE-A912-4902-9064-AE70A491609E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{BEC21941-B947-480A-A7E6-7B63159DE119}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="140">
   <si>
     <t>JobOfferUsers</t>
   </si>
@@ -391,13 +391,73 @@
   </si>
   <si>
     <t>AnnualSalary</t>
+  </si>
+  <si>
+    <t>CompensationBenefits</t>
+  </si>
+  <si>
+    <t>ItemName</t>
+  </si>
+  <si>
+    <t>PackageName</t>
+  </si>
+  <si>
+    <t>Amount</t>
+  </si>
+  <si>
+    <t>PackageId</t>
+  </si>
+  <si>
+    <t>TypeId</t>
+  </si>
+  <si>
+    <t>IsTaxable</t>
+  </si>
+  <si>
+    <t>IsRecurring</t>
+  </si>
+  <si>
+    <t>FrequencyName</t>
+  </si>
+  <si>
+    <t>FrequencyId</t>
+  </si>
+  <si>
+    <t>DisplayOrder</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IsActive </t>
+  </si>
+  <si>
+    <t>Tax</t>
+  </si>
+  <si>
+    <t>Multiplier</t>
+  </si>
+  <si>
+    <t>CompBenTypes</t>
+  </si>
+  <si>
+    <t>CompBenPackages</t>
+  </si>
+  <si>
+    <t>Frequencies</t>
+  </si>
+  <si>
+    <t>CompBenItems</t>
+  </si>
+  <si>
+    <t>CompBenItemId</t>
+  </si>
+  <si>
+    <t>ItemDescription</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -412,6 +472,17 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
     </font>
   </fonts>
   <fills count="2">
@@ -434,9 +505,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -772,7 +849,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9EF47D5C-035D-491F-B6E5-626F15CDCBDA}">
   <dimension ref="B2:J51"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="2" max="2" width="16.54296875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14.90625" bestFit="1" customWidth="1"/>
@@ -781,7 +858,7 @@
     <col min="10" max="10" width="16.6328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:10">
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
@@ -798,7 +875,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="3" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:10">
       <c r="B3" t="s">
         <v>1</v>
       </c>
@@ -815,7 +892,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:10">
       <c r="B4" t="s">
         <v>47</v>
       </c>
@@ -832,7 +909,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:10">
       <c r="B5" t="s">
         <v>2</v>
       </c>
@@ -849,7 +926,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="6" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:10">
       <c r="B6" t="s">
         <v>3</v>
       </c>
@@ -863,7 +940,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:10">
       <c r="B9" s="1" t="s">
         <v>4</v>
       </c>
@@ -874,7 +951,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:10">
       <c r="B10" t="s">
         <v>1</v>
       </c>
@@ -885,7 +962,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:10">
       <c r="B11" t="s">
         <v>5</v>
       </c>
@@ -896,7 +973,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="12" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:10">
       <c r="B12" t="s">
         <v>6</v>
       </c>
@@ -907,7 +984,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:10">
       <c r="D13" t="s">
         <v>10</v>
       </c>
@@ -915,32 +992,32 @@
         <v>17</v>
       </c>
     </row>
-    <row r="14" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:10">
       <c r="F14" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="15" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:10">
       <c r="F15" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="16" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:10">
       <c r="F16" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:6">
       <c r="F17" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:6">
       <c r="F18" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:6">
       <c r="B21" s="1" t="s">
         <v>22</v>
       </c>
@@ -951,7 +1028,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:6">
       <c r="B22" t="s">
         <v>1</v>
       </c>
@@ -962,7 +1039,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:6">
       <c r="B23" t="s">
         <v>23</v>
       </c>
@@ -973,7 +1050,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:6">
       <c r="B24" t="s">
         <v>24</v>
       </c>
@@ -984,107 +1061,107 @@
         <v>26</v>
       </c>
     </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:6">
       <c r="F25" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:6">
       <c r="F26" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:6">
       <c r="F27" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:6">
       <c r="B30" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="31" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:6">
       <c r="B31" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:6">
       <c r="B32" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="33" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:2">
       <c r="B33" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="34" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:2">
       <c r="B34" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="37" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:2">
       <c r="B37" s="1" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="38" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="38" spans="2:2">
       <c r="B38" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="39" spans="2:2">
       <c r="B39" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="40" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="40" spans="2:2">
       <c r="B40" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="41" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="41" spans="2:2">
       <c r="B41" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="42" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="42" spans="2:2">
       <c r="B42" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="43" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="43" spans="2:2">
       <c r="B43" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="44" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="44" spans="2:2">
       <c r="B44" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="45" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="45" spans="2:2">
       <c r="B45" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="48" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="48" spans="2:2">
       <c r="B48" s="1" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="49" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="49" spans="2:2">
       <c r="B49" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="50" spans="2:2">
       <c r="B50" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="51" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="51" spans="2:2">
       <c r="B51" t="s">
         <v>50</v>
       </c>
@@ -1097,14 +1174,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{026B99F0-FC57-47AB-AF03-F4ABCCD02BF2}">
   <dimension ref="B2:H16"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="2" max="2" width="22.54296875" customWidth="1"/>
     <col min="4" max="4" width="24.453125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="18.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:8">
       <c r="B2" s="1" t="s">
         <v>53</v>
       </c>
@@ -1118,7 +1195,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:8">
       <c r="B3" t="s">
         <v>1</v>
       </c>
@@ -1132,7 +1209,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:8">
       <c r="B4" t="s">
         <v>54</v>
       </c>
@@ -1146,7 +1223,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:8">
       <c r="B5" t="s">
         <v>55</v>
       </c>
@@ -1157,7 +1234,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="6" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:8">
       <c r="B6" t="s">
         <v>56</v>
       </c>
@@ -1168,7 +1245,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:8">
       <c r="B7" t="s">
         <v>3</v>
       </c>
@@ -1179,7 +1256,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:8">
       <c r="B8" t="s">
         <v>57</v>
       </c>
@@ -1190,7 +1267,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="9" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:8">
       <c r="B9" t="s">
         <v>58</v>
       </c>
@@ -1201,7 +1278,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:8">
       <c r="B10" t="s">
         <v>59</v>
       </c>
@@ -1212,7 +1289,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="11" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:8">
       <c r="B11" t="s">
         <v>60</v>
       </c>
@@ -1223,7 +1300,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="12" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:8">
       <c r="B12" t="s">
         <v>61</v>
       </c>
@@ -1231,22 +1308,22 @@
         <v>73</v>
       </c>
     </row>
-    <row r="13" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:8">
       <c r="B13" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="14" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:8">
       <c r="B14" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="15" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:8">
       <c r="B15" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="16" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:8">
       <c r="B16" t="s">
         <v>64</v>
       </c>
@@ -1259,7 +1336,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9AD6FEA5-0945-4178-A2F8-A72772503D4A}">
   <dimension ref="B2:J18"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="2" max="2" width="21.36328125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.1796875" bestFit="1" customWidth="1"/>
@@ -1268,7 +1345,7 @@
     <col min="10" max="10" width="19.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:10">
       <c r="B2" s="1" t="s">
         <v>66</v>
       </c>
@@ -1285,7 +1362,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="3" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:10">
       <c r="B3" t="s">
         <v>1</v>
       </c>
@@ -1302,7 +1379,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:10">
       <c r="B4" t="s">
         <v>16</v>
       </c>
@@ -1319,7 +1396,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:10">
       <c r="B5" t="s">
         <v>74</v>
       </c>
@@ -1336,7 +1413,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="6" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:10">
       <c r="B6" t="s">
         <v>109</v>
       </c>
@@ -1350,7 +1427,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:10">
       <c r="B7" t="s">
         <v>110</v>
       </c>
@@ -1358,7 +1435,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="8" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:10">
       <c r="B8" t="s">
         <v>92</v>
       </c>
@@ -1366,7 +1443,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:10">
       <c r="B9" t="s">
         <v>75</v>
       </c>
@@ -1374,7 +1451,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="10" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:10">
       <c r="B10" t="s">
         <v>89</v>
       </c>
@@ -1382,7 +1459,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:10">
       <c r="B11" t="s">
         <v>90</v>
       </c>
@@ -1390,37 +1467,37 @@
         <v>100</v>
       </c>
     </row>
-    <row r="12" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:10">
       <c r="H12" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="13" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:10">
       <c r="H13" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="14" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:10">
       <c r="H14" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="15" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:10">
       <c r="H15" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="16" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:10">
       <c r="H16" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="17" spans="8:8" x14ac:dyDescent="0.35">
+    <row r="17" spans="8:8">
       <c r="H17" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="18" spans="8:8" x14ac:dyDescent="0.35">
+    <row r="18" spans="8:8">
       <c r="H18" t="s">
         <v>104</v>
       </c>
@@ -1432,109 +1509,211 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D3A9745-558A-479E-B1B2-9C6EC5EEDA6F}">
-  <dimension ref="B2:D15"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="B2:J15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="2" max="2" width="20.26953125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="19.90625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="28.81640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="23.81640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="25.6328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:10">
       <c r="B2" s="1" t="s">
         <v>66</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="3" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="F2" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="3" spans="2:10">
       <c r="B3" t="s">
         <v>1</v>
       </c>
       <c r="D3" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="F3" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" t="s">
+        <v>1</v>
+      </c>
+      <c r="J3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="2:10">
       <c r="B4" t="s">
         <v>16</v>
       </c>
       <c r="D4" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="5" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="F4" t="s">
+        <v>83</v>
+      </c>
+      <c r="H4" t="s">
+        <v>124</v>
+      </c>
+      <c r="J4" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="5" spans="2:10">
       <c r="B5" t="s">
         <v>74</v>
       </c>
       <c r="D5" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="6" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="H5" t="s">
+        <v>138</v>
+      </c>
+      <c r="J5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" spans="2:10">
       <c r="B6" t="s">
         <v>109</v>
       </c>
       <c r="D6" t="s">
         <v>113</v>
       </c>
-    </row>
-    <row r="7" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="F6" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="7" spans="2:10">
       <c r="B7" t="s">
         <v>110</v>
       </c>
       <c r="D7" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="8" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="F7" t="s">
+        <v>1</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="8" spans="2:10">
       <c r="B8" t="s">
         <v>92</v>
       </c>
       <c r="D8" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="9" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="F8" t="s">
+        <v>128</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="J8" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="2:10">
       <c r="B9" t="s">
         <v>75</v>
       </c>
       <c r="D9" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="10" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="F9" t="s">
+        <v>133</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="J9" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="10" spans="2:10">
       <c r="B10" t="s">
         <v>89</v>
       </c>
       <c r="D10" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="11" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="H10" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="J10" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="11" spans="2:10">
       <c r="B11" t="s">
         <v>90</v>
       </c>
       <c r="D11" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="12" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="F11" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="J11" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="12" spans="2:10">
       <c r="D12" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="13" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="F12" t="s">
+        <v>1</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="13" spans="2:10">
       <c r="D13" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row r="14" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="F13" t="s">
+        <v>87</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="14" spans="2:10">
       <c r="D14" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="15" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="F14" t="s">
+        <v>88</v>
+      </c>
+      <c r="H14" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="15" spans="2:10">
       <c r="D15" t="s">
         <v>90</v>
       </c>

--- a/Documents/DBdesign.xlsx
+++ b/Documents/DBdesign.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitLab\joboffer\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B20B1CAE-A912-4902-9064-AE70A491609E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E728A8A2-55D4-4C19-85E5-476B68488387}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{BEC21941-B947-480A-A7E6-7B63159DE119}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="155">
   <si>
     <t>JobOfferUsers</t>
   </si>
@@ -451,6 +451,51 @@
   </si>
   <si>
     <t>ItemDescription</t>
+  </si>
+  <si>
+    <t>ValidationStatusId</t>
+  </si>
+  <si>
+    <t>JobOfferAnalysis</t>
+  </si>
+  <si>
+    <t>JobOfferAnalysisId</t>
+  </si>
+  <si>
+    <t>AnalysisNotes</t>
+  </si>
+  <si>
+    <t>RecommendProposalId</t>
+  </si>
+  <si>
+    <t>BestProposalSalary</t>
+  </si>
+  <si>
+    <t>SalaryMatrixBand</t>
+  </si>
+  <si>
+    <t>JobLevelId</t>
+  </si>
+  <si>
+    <t>JobFamilyId</t>
+  </si>
+  <si>
+    <t>PositionGradeId</t>
+  </si>
+  <si>
+    <t>BandMinimum</t>
+  </si>
+  <si>
+    <t>BandMidpoint</t>
+  </si>
+  <si>
+    <t>BandMaximum</t>
+  </si>
+  <si>
+    <t>BelowBandFlagEnabled</t>
+  </si>
+  <si>
+    <t>AboveBandFlagEnabled</t>
   </si>
 </sst>
 </file>
@@ -1509,12 +1554,12 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D3A9745-558A-479E-B1B2-9C6EC5EEDA6F}">
-  <dimension ref="B2:J15"/>
+  <dimension ref="B2:J28"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="2" max="2" width="20.26953125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="19.90625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="28.81640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.453125" customWidth="1"/>
     <col min="8" max="8" width="23.81640625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="25.6328125" bestFit="1" customWidth="1"/>
   </cols>
@@ -1650,9 +1695,6 @@
       </c>
     </row>
     <row r="10" spans="2:10">
-      <c r="B10" t="s">
-        <v>89</v>
-      </c>
       <c r="D10" t="s">
         <v>116</v>
       </c>
@@ -1664,9 +1706,6 @@
       </c>
     </row>
     <row r="11" spans="2:10">
-      <c r="B11" t="s">
-        <v>90</v>
-      </c>
       <c r="D11" t="s">
         <v>117</v>
       </c>
@@ -1682,7 +1721,7 @@
     </row>
     <row r="12" spans="2:10">
       <c r="D12" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F12" t="s">
         <v>1</v>
@@ -1693,7 +1732,7 @@
     </row>
     <row r="13" spans="2:10">
       <c r="D13" t="s">
-        <v>119</v>
+        <v>140</v>
       </c>
       <c r="F13" t="s">
         <v>87</v>
@@ -1704,7 +1743,7 @@
     </row>
     <row r="14" spans="2:10">
       <c r="D14" t="s">
-        <v>89</v>
+        <v>118</v>
       </c>
       <c r="F14" t="s">
         <v>88</v>
@@ -1715,7 +1754,92 @@
     </row>
     <row r="15" spans="2:10">
       <c r="D15" t="s">
-        <v>90</v>
+        <v>142</v>
+      </c>
+    </row>
+    <row r="18" spans="2:4">
+      <c r="B18" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="19" spans="2:4">
+      <c r="B19" t="s">
+        <v>1</v>
+      </c>
+      <c r="D19" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="2:4">
+      <c r="B20" t="s">
+        <v>92</v>
+      </c>
+      <c r="D20" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="21" spans="2:4">
+      <c r="B21" t="s">
+        <v>147</v>
+      </c>
+      <c r="D21" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="22" spans="2:4">
+      <c r="B22" t="s">
+        <v>148</v>
+      </c>
+      <c r="D22" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="23" spans="2:4">
+      <c r="B23" t="s">
+        <v>149</v>
+      </c>
+      <c r="D23" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="24" spans="2:4">
+      <c r="B24" t="s">
+        <v>150</v>
+      </c>
+      <c r="D24" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="25" spans="2:4">
+      <c r="B25" t="s">
+        <v>151</v>
+      </c>
+      <c r="D25" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="26" spans="2:4">
+      <c r="B26" t="s">
+        <v>152</v>
+      </c>
+      <c r="D26" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="27" spans="2:4">
+      <c r="B27" t="s">
+        <v>153</v>
+      </c>
+      <c r="D27" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="28" spans="2:4">
+      <c r="B28" t="s">
+        <v>154</v>
       </c>
     </row>
   </sheetData>

--- a/Documents/DBdesign.xlsx
+++ b/Documents/DBdesign.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitLab\joboffer\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E728A8A2-55D4-4C19-85E5-476B68488387}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE0262FC-5D1F-4BEE-83FF-F4FF374E7468}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{BEC21941-B947-480A-A7E6-7B63159DE119}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" activeTab="3" xr2:uid="{BEC21941-B947-480A-A7E6-7B63159DE119}"/>
   </bookViews>
   <sheets>
     <sheet name="RBAC+ABAC" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="158">
   <si>
     <t>JobOfferUsers</t>
   </si>
@@ -496,6 +496,15 @@
   </si>
   <si>
     <t>AboveBandFlagEnabled</t>
+  </si>
+  <si>
+    <t>ProposalStatus</t>
+  </si>
+  <si>
+    <t>StatusName</t>
+  </si>
+  <si>
+    <t>ProposalStatusId</t>
   </si>
 </sst>
 </file>
@@ -1757,31 +1766,45 @@
         <v>142</v>
       </c>
     </row>
-    <row r="18" spans="2:4">
+    <row r="16" spans="2:10">
+      <c r="D16" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="18" spans="2:6">
       <c r="B18" s="1" t="s">
         <v>146</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="19" spans="2:4">
+      <c r="F18" s="1" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="19" spans="2:6">
       <c r="B19" t="s">
         <v>1</v>
       </c>
       <c r="D19" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="20" spans="2:4">
+      <c r="F19" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="2:6">
       <c r="B20" t="s">
         <v>92</v>
       </c>
       <c r="D20" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="21" spans="2:4">
+      <c r="F20" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="21" spans="2:6">
       <c r="B21" t="s">
         <v>147</v>
       </c>
@@ -1789,7 +1812,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="22" spans="2:4">
+    <row r="22" spans="2:6">
       <c r="B22" t="s">
         <v>148</v>
       </c>
@@ -1797,7 +1820,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="23" spans="2:4">
+    <row r="23" spans="2:6">
       <c r="B23" t="s">
         <v>149</v>
       </c>
@@ -1805,7 +1828,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="24" spans="2:4">
+    <row r="24" spans="2:6">
       <c r="B24" t="s">
         <v>150</v>
       </c>
@@ -1813,7 +1836,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="25" spans="2:4">
+    <row r="25" spans="2:6">
       <c r="B25" t="s">
         <v>151</v>
       </c>
@@ -1821,7 +1844,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="26" spans="2:4">
+    <row r="26" spans="2:6">
       <c r="B26" t="s">
         <v>152</v>
       </c>
@@ -1829,7 +1852,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="27" spans="2:4">
+    <row r="27" spans="2:6">
       <c r="B27" t="s">
         <v>153</v>
       </c>
@@ -1837,7 +1860,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="28" spans="2:4">
+    <row r="28" spans="2:6">
       <c r="B28" t="s">
         <v>154</v>
       </c>

--- a/Documents/DBdesign.xlsx
+++ b/Documents/DBdesign.xlsx
@@ -1,22 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitLab\joboffer\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE0262FC-5D1F-4BEE-83FF-F4FF374E7468}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C95BE28A-057A-4D98-8CFF-169791647D95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" activeTab="3" xr2:uid="{BEC21941-B947-480A-A7E6-7B63159DE119}"/>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{BEC21941-B947-480A-A7E6-7B63159DE119}"/>
   </bookViews>
   <sheets>
     <sheet name="RBAC+ABAC" sheetId="1" r:id="rId1"/>
     <sheet name="MSForms" sheetId="2" r:id="rId2"/>
     <sheet name="Company Setup" sheetId="3" r:id="rId3"/>
     <sheet name="Analysis" sheetId="4" r:id="rId4"/>
+    <sheet name="Approval" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -31,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="163">
   <si>
     <t>JobOfferUsers</t>
   </si>
@@ -505,6 +506,21 @@
   </si>
   <si>
     <t>ProposalStatusId</t>
+  </si>
+  <si>
+    <t>HRODJOProposal</t>
+  </si>
+  <si>
+    <t>JobOfferProposalId</t>
+  </si>
+  <si>
+    <t>DHJOProposal</t>
+  </si>
+  <si>
+    <t>PresidentJOProposal</t>
+  </si>
+  <si>
+    <t>Comments</t>
   </si>
 </sst>
 </file>
@@ -1868,4 +1884,223 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{852D4CF3-1038-42B3-A697-EC51612C14F3}">
+  <dimension ref="B2:J18"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
+  <cols>
+    <col min="2" max="2" width="19.90625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.08984375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.453125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19.90625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="20.26953125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:10">
+      <c r="B2" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="3" spans="2:10">
+      <c r="B3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F3" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" t="s">
+        <v>1</v>
+      </c>
+      <c r="J3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="2:10">
+      <c r="B4" t="s">
+        <v>106</v>
+      </c>
+      <c r="D4" t="s">
+        <v>159</v>
+      </c>
+      <c r="F4" t="s">
+        <v>156</v>
+      </c>
+      <c r="H4" t="s">
+        <v>106</v>
+      </c>
+      <c r="J4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="2:10">
+      <c r="B5" t="s">
+        <v>112</v>
+      </c>
+      <c r="D5" t="s">
+        <v>157</v>
+      </c>
+      <c r="H5" t="s">
+        <v>124</v>
+      </c>
+      <c r="J5" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="6" spans="2:10">
+      <c r="B6" t="s">
+        <v>113</v>
+      </c>
+      <c r="D6" t="s">
+        <v>162</v>
+      </c>
+      <c r="H6" t="s">
+        <v>60</v>
+      </c>
+      <c r="J6" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="7" spans="2:10">
+      <c r="B7" t="s">
+        <v>114</v>
+      </c>
+      <c r="H7" t="s">
+        <v>145</v>
+      </c>
+      <c r="J7" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="8" spans="2:10">
+      <c r="B8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="H8" t="s">
+        <v>140</v>
+      </c>
+      <c r="J8" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="9" spans="2:10">
+      <c r="B9" t="s">
+        <v>115</v>
+      </c>
+      <c r="D9" t="s">
+        <v>1</v>
+      </c>
+      <c r="F9" t="s">
+        <v>1</v>
+      </c>
+      <c r="H9" t="s">
+        <v>143</v>
+      </c>
+      <c r="J9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="10" spans="2:10">
+      <c r="B10" t="s">
+        <v>116</v>
+      </c>
+      <c r="D10" t="s">
+        <v>159</v>
+      </c>
+      <c r="F10" t="s">
+        <v>94</v>
+      </c>
+      <c r="H10" t="s">
+        <v>144</v>
+      </c>
+      <c r="J10" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="11" spans="2:10">
+      <c r="B11" t="s">
+        <v>117</v>
+      </c>
+      <c r="D11" t="s">
+        <v>157</v>
+      </c>
+      <c r="F11" t="s">
+        <v>95</v>
+      </c>
+      <c r="H11" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="12" spans="2:10">
+      <c r="B12" t="s">
+        <v>119</v>
+      </c>
+      <c r="D12" t="s">
+        <v>162</v>
+      </c>
+      <c r="F12" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="13" spans="2:10">
+      <c r="B13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="14" spans="2:10">
+      <c r="B14" t="s">
+        <v>118</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="15" spans="2:10">
+      <c r="B15" t="s">
+        <v>142</v>
+      </c>
+      <c r="D15" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="2:10">
+      <c r="D16" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="17" spans="4:4">
+      <c r="D17" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="18" spans="4:4">
+      <c r="D18" t="s">
+        <v>162</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Documents/DBdesign.xlsx
+++ b/Documents/DBdesign.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitLab\joboffer\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C95BE28A-057A-4D98-8CFF-169791647D95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26C11153-8AF5-4900-8E61-05CD1C4F3905}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{BEC21941-B947-480A-A7E6-7B63159DE119}"/>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="7" xr2:uid="{BEC21941-B947-480A-A7E6-7B63159DE119}"/>
   </bookViews>
   <sheets>
     <sheet name="RBAC+ABAC" sheetId="1" r:id="rId1"/>
@@ -18,8 +18,12 @@
     <sheet name="Company Setup" sheetId="3" r:id="rId3"/>
     <sheet name="Analysis" sheetId="4" r:id="rId4"/>
     <sheet name="Approval" sheetId="5" r:id="rId5"/>
+    <sheet name="Discussion" sheetId="6" r:id="rId6"/>
+    <sheet name="WorkFlow" sheetId="8" r:id="rId7"/>
+    <sheet name="ReDesign" sheetId="9" r:id="rId8"/>
   </sheets>
   <calcPr calcId="181029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -32,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="441" uniqueCount="231">
   <si>
     <t>JobOfferUsers</t>
   </si>
@@ -521,6 +525,210 @@
   </si>
   <si>
     <t>Comments</t>
+  </si>
+  <si>
+    <t>JoOfferWorkFlow</t>
+  </si>
+  <si>
+    <t>DiscussionDate</t>
+  </si>
+  <si>
+    <t>ChannelTypes</t>
+  </si>
+  <si>
+    <t>ChannelName</t>
+  </si>
+  <si>
+    <t>ChannelTypeId</t>
+  </si>
+  <si>
+    <t>ResponseName</t>
+  </si>
+  <si>
+    <t>CandidateResponses</t>
+  </si>
+  <si>
+    <t>CandidateResponseId</t>
+  </si>
+  <si>
+    <t>CandidateFeedback</t>
+  </si>
+  <si>
+    <t>Icon</t>
+  </si>
+  <si>
+    <t>DiscussionSteps</t>
+  </si>
+  <si>
+    <t>StepName</t>
+  </si>
+  <si>
+    <t>DiscussionStepId</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Icon </t>
+  </si>
+  <si>
+    <t>DiscussionEntries</t>
+  </si>
+  <si>
+    <t>TANotes</t>
+  </si>
+  <si>
+    <t>NextWorkFlowStatusId</t>
+  </si>
+  <si>
+    <t>CandidateMSFormRequestId</t>
+  </si>
+  <si>
+    <t>WorkFlowActions</t>
+  </si>
+  <si>
+    <t>ActionName</t>
+  </si>
+  <si>
+    <t>WorkFlowActionId</t>
+  </si>
+  <si>
+    <t>CandidateApplicationStatus</t>
+  </si>
+  <si>
+    <t>JobOffers</t>
+  </si>
+  <si>
+    <t>Documents</t>
+  </si>
+  <si>
+    <t>RequestId</t>
+  </si>
+  <si>
+    <t>DocumentId</t>
+  </si>
+  <si>
+    <t>MatrixId</t>
+  </si>
+  <si>
+    <t>JoOfferId</t>
+  </si>
+  <si>
+    <t>Employer</t>
+  </si>
+  <si>
+    <t>Contact</t>
+  </si>
+  <si>
+    <t>Expected</t>
+  </si>
+  <si>
+    <t>RefNum</t>
+  </si>
+  <si>
+    <t>Requests</t>
+  </si>
+  <si>
+    <t>Reminder2</t>
+  </si>
+  <si>
+    <t>Reminder1</t>
+  </si>
+  <si>
+    <t>ActionId</t>
+  </si>
+  <si>
+    <t>WorkFlow</t>
+  </si>
+  <si>
+    <t>Proposal</t>
+  </si>
+  <si>
+    <t>JobOfferId</t>
+  </si>
+  <si>
+    <t>BandId</t>
+  </si>
+  <si>
+    <t>Option</t>
+  </si>
+  <si>
+    <t>Current</t>
+  </si>
+  <si>
+    <t>Increase</t>
+  </si>
+  <si>
+    <t>Annual</t>
+  </si>
+  <si>
+    <t>Legals</t>
+  </si>
+  <si>
+    <t>LegalId</t>
+  </si>
+  <si>
+    <t>Recommend</t>
+  </si>
+  <si>
+    <t>Approvals</t>
+  </si>
+  <si>
+    <t>ProposalId</t>
+  </si>
+  <si>
+    <t>ApproverType</t>
+  </si>
+  <si>
+    <t>ApproveBy</t>
+  </si>
+  <si>
+    <t>ApproveAt</t>
+  </si>
+  <si>
+    <t>Discussions</t>
+  </si>
+  <si>
+    <t>DiscussAt</t>
+  </si>
+  <si>
+    <t>ResponseId</t>
+  </si>
+  <si>
+    <t>FeedBack</t>
+  </si>
+  <si>
+    <t>StepId</t>
+  </si>
+  <si>
+    <t>MName</t>
+  </si>
+  <si>
+    <t>FName</t>
+  </si>
+  <si>
+    <t>LName</t>
+  </si>
+  <si>
+    <t>LstPosition</t>
+  </si>
+  <si>
+    <t>ApplyFor</t>
+  </si>
+  <si>
+    <t>Subject</t>
+  </si>
+  <si>
+    <t>Message</t>
+  </si>
+  <si>
+    <t>SentAt</t>
+  </si>
+  <si>
+    <t>DueAt</t>
+  </si>
+  <si>
+    <t>Propose</t>
+  </si>
+  <si>
+    <t>Salary</t>
   </si>
 </sst>
 </file>
@@ -1408,7 +1616,7 @@
   <dimension ref="B2:J18"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="21.36328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.7265625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.1796875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="14" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="15.6328125" bestFit="1" customWidth="1"/>
@@ -1548,16 +1756,25 @@
       </c>
     </row>
     <row r="14" spans="2:10">
+      <c r="B14" s="1" t="s">
+        <v>184</v>
+      </c>
       <c r="H14" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="15" spans="2:10">
+      <c r="B15" t="s">
+        <v>1</v>
+      </c>
       <c r="H15" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="16" spans="2:10">
+      <c r="B16" t="s">
+        <v>156</v>
+      </c>
       <c r="H16" t="s">
         <v>89</v>
       </c>
@@ -2103,4 +2320,584 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{580FB0E5-89D5-4955-8D17-6E97D145D9F7}">
+  <dimension ref="B2:H16"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
+  <cols>
+    <col min="2" max="2" width="19.90625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.36328125" customWidth="1"/>
+    <col min="6" max="6" width="19.90625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.81640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:8">
+      <c r="B2" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="3" spans="2:8">
+      <c r="B3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F3" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="2:8">
+      <c r="B4" t="s">
+        <v>106</v>
+      </c>
+      <c r="D4" t="s">
+        <v>94</v>
+      </c>
+      <c r="F4" t="s">
+        <v>106</v>
+      </c>
+      <c r="H4" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="5" spans="2:8">
+      <c r="B5" t="s">
+        <v>112</v>
+      </c>
+      <c r="D5" t="s">
+        <v>95</v>
+      </c>
+      <c r="F5" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="6" spans="2:8">
+      <c r="B6" t="s">
+        <v>113</v>
+      </c>
+      <c r="D6" t="s">
+        <v>130</v>
+      </c>
+      <c r="F6" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="7" spans="2:8">
+      <c r="B7" t="s">
+        <v>114</v>
+      </c>
+      <c r="F7" t="s">
+        <v>167</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="8" spans="2:8">
+      <c r="B8" t="s">
+        <v>20</v>
+      </c>
+      <c r="F8" t="s">
+        <v>170</v>
+      </c>
+      <c r="H8" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="2:8">
+      <c r="B9" t="s">
+        <v>115</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="F9" t="s">
+        <v>178</v>
+      </c>
+      <c r="H9" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="10" spans="2:8">
+      <c r="B10" t="s">
+        <v>116</v>
+      </c>
+      <c r="D10" t="s">
+        <v>1</v>
+      </c>
+      <c r="F10" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="11" spans="2:8">
+      <c r="B11" t="s">
+        <v>117</v>
+      </c>
+      <c r="D11" t="s">
+        <v>106</v>
+      </c>
+      <c r="F11" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="12" spans="2:8">
+      <c r="B12" t="s">
+        <v>119</v>
+      </c>
+      <c r="D12" t="s">
+        <v>142</v>
+      </c>
+      <c r="F12" t="s">
+        <v>89</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="13" spans="2:8">
+      <c r="B13" t="s">
+        <v>140</v>
+      </c>
+      <c r="D13" t="s">
+        <v>107</v>
+      </c>
+      <c r="F13" t="s">
+        <v>175</v>
+      </c>
+      <c r="H13" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="2:8">
+      <c r="B14" t="s">
+        <v>118</v>
+      </c>
+      <c r="D14" t="s">
+        <v>179</v>
+      </c>
+      <c r="H14" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="15" spans="2:8">
+      <c r="B15" t="s">
+        <v>142</v>
+      </c>
+      <c r="D15" t="s">
+        <v>180</v>
+      </c>
+      <c r="H15" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="16" spans="2:8">
+      <c r="F16" s="1"/>
+      <c r="H16" t="s">
+        <v>176</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{543B08D0-87A8-44D6-9F83-94933D8C9C17}">
+  <dimension ref="B2:D11"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
+  <cols>
+    <col min="2" max="2" width="24.1796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.26953125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:4">
+      <c r="B2" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="3" spans="2:4">
+      <c r="B3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="2:4">
+      <c r="B4" t="s">
+        <v>106</v>
+      </c>
+      <c r="D4" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="5" spans="2:4">
+      <c r="B5" t="s">
+        <v>142</v>
+      </c>
+      <c r="D5" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="6" spans="2:4">
+      <c r="B6" t="s">
+        <v>107</v>
+      </c>
+      <c r="D6" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="7" spans="2:4">
+      <c r="B7" t="s">
+        <v>180</v>
+      </c>
+      <c r="D7" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="8" spans="2:4">
+      <c r="B8" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="9" spans="2:4">
+      <c r="D9" s="1" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="10" spans="2:4">
+      <c r="D10" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="2:4">
+      <c r="D11" t="s">
+        <v>182</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D794D288-BDD7-47B9-8549-02ED03290623}">
+  <dimension ref="B2:M25"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
+  <cols>
+    <col min="2" max="2" width="18.453125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17" customWidth="1"/>
+    <col min="6" max="6" width="15" customWidth="1"/>
+    <col min="8" max="8" width="15.6328125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="19.90625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.7265625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="19.90625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:13">
+      <c r="B2" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="3" spans="2:13">
+      <c r="B3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F3" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" t="s">
+        <v>1</v>
+      </c>
+      <c r="J3" t="s">
+        <v>1</v>
+      </c>
+      <c r="K3" t="s">
+        <v>1</v>
+      </c>
+      <c r="M3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="2:13">
+      <c r="B4" t="s">
+        <v>221</v>
+      </c>
+      <c r="D4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H4" t="s">
+        <v>16</v>
+      </c>
+      <c r="J4" t="s">
+        <v>201</v>
+      </c>
+      <c r="K4" t="s">
+        <v>211</v>
+      </c>
+      <c r="M4" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="5" spans="2:13">
+      <c r="B5" t="s">
+        <v>220</v>
+      </c>
+      <c r="D5" t="s">
+        <v>227</v>
+      </c>
+      <c r="F5" t="s">
+        <v>187</v>
+      </c>
+      <c r="H5" t="s">
+        <v>8</v>
+      </c>
+      <c r="J5" t="s">
+        <v>202</v>
+      </c>
+      <c r="K5" t="s">
+        <v>69</v>
+      </c>
+      <c r="M5" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="6" spans="2:13">
+      <c r="B6" t="s">
+        <v>222</v>
+      </c>
+      <c r="D6" t="s">
+        <v>228</v>
+      </c>
+      <c r="F6" t="s">
+        <v>76</v>
+      </c>
+      <c r="H6" t="s">
+        <v>52</v>
+      </c>
+      <c r="J6" t="s">
+        <v>203</v>
+      </c>
+      <c r="K6" t="s">
+        <v>162</v>
+      </c>
+      <c r="M6" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="7" spans="2:13">
+      <c r="B7" t="s">
+        <v>3</v>
+      </c>
+      <c r="D7" t="s">
+        <v>225</v>
+      </c>
+      <c r="F7" t="s">
+        <v>77</v>
+      </c>
+      <c r="H7" t="s">
+        <v>189</v>
+      </c>
+      <c r="J7" t="s">
+        <v>204</v>
+      </c>
+      <c r="K7" t="s">
+        <v>125</v>
+      </c>
+      <c r="M7" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="8" spans="2:13">
+      <c r="B8" t="s">
+        <v>192</v>
+      </c>
+      <c r="D8" t="s">
+        <v>226</v>
+      </c>
+      <c r="F8" t="s">
+        <v>78</v>
+      </c>
+      <c r="J8" t="s">
+        <v>229</v>
+      </c>
+      <c r="K8" t="s">
+        <v>213</v>
+      </c>
+      <c r="M8" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="9" spans="2:13">
+      <c r="B9" t="s">
+        <v>224</v>
+      </c>
+      <c r="D9" t="s">
+        <v>197</v>
+      </c>
+      <c r="F9" t="s">
+        <v>79</v>
+      </c>
+      <c r="J9" t="s">
+        <v>116</v>
+      </c>
+      <c r="K9" t="s">
+        <v>214</v>
+      </c>
+      <c r="M9" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="10" spans="2:13">
+      <c r="B10" t="s">
+        <v>223</v>
+      </c>
+      <c r="D10" t="s">
+        <v>196</v>
+      </c>
+      <c r="J10" t="s">
+        <v>205</v>
+      </c>
+      <c r="M10" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="11" spans="2:13">
+      <c r="B11" t="s">
+        <v>191</v>
+      </c>
+      <c r="J11" t="s">
+        <v>206</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="M11" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="12" spans="2:13">
+      <c r="B12" t="s">
+        <v>230</v>
+      </c>
+      <c r="J12" t="s">
+        <v>209</v>
+      </c>
+      <c r="K12" t="s">
+        <v>1</v>
+      </c>
+      <c r="M12" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="13" spans="2:13">
+      <c r="B13" t="s">
+        <v>193</v>
+      </c>
+      <c r="K13" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="17" spans="2:4">
+      <c r="D17" s="1" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="18" spans="2:4">
+      <c r="B18" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="D18" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="2:4">
+      <c r="B19" t="s">
+        <v>1</v>
+      </c>
+      <c r="D19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="20" spans="2:4">
+      <c r="B20" t="s">
+        <v>194</v>
+      </c>
+      <c r="D20" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="21" spans="2:4">
+      <c r="B21" t="s">
+        <v>69</v>
+      </c>
+      <c r="D21" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="22" spans="2:4">
+      <c r="B22" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="23" spans="2:4">
+      <c r="B23" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="24" spans="2:4">
+      <c r="B24" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="25" spans="2:4">
+      <c r="B25" t="s">
+        <v>208</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Documents/DBdesign.xlsx
+++ b/Documents/DBdesign.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitLab\joboffer\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26C11153-8AF5-4900-8E61-05CD1C4F3905}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F380A88C-3631-4358-AEF4-22CCBFBF3F1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="7" xr2:uid="{BEC21941-B947-480A-A7E6-7B63159DE119}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" firstSheet="1" activeTab="7" xr2:uid="{BEC21941-B947-480A-A7E6-7B63159DE119}"/>
   </bookViews>
   <sheets>
     <sheet name="RBAC+ABAC" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,6 @@
     <sheet name="ReDesign" sheetId="9" r:id="rId8"/>
   </sheets>
   <calcPr calcId="181029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="441" uniqueCount="231">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="443" uniqueCount="231">
   <si>
     <t>JobOfferUsers</t>
   </si>
@@ -659,9 +658,6 @@
     <t>Annual</t>
   </si>
   <si>
-    <t>Legals</t>
-  </si>
-  <si>
     <t>LegalId</t>
   </si>
   <si>
@@ -729,6 +725,9 @@
   </si>
   <si>
     <t>Salary</t>
+  </si>
+  <si>
+    <t>JobPositionId</t>
   </si>
 </sst>
 </file>
@@ -2623,16 +2622,16 @@
         <v>186</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>207</v>
+        <v>7</v>
       </c>
       <c r="J2" s="1" t="s">
         <v>200</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="3" spans="2:13">
@@ -2660,7 +2659,7 @@
     </row>
     <row r="4" spans="2:13">
       <c r="B4" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D4" t="s">
         <v>16</v>
@@ -2675,7 +2674,7 @@
         <v>201</v>
       </c>
       <c r="K4" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="M4" t="s">
         <v>201</v>
@@ -2683,10 +2682,10 @@
     </row>
     <row r="5" spans="2:13">
       <c r="B5" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D5" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F5" t="s">
         <v>187</v>
@@ -2701,15 +2700,15 @@
         <v>69</v>
       </c>
       <c r="M5" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="6" spans="2:13">
       <c r="B6" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D6" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F6" t="s">
         <v>76</v>
@@ -2724,7 +2723,7 @@
         <v>162</v>
       </c>
       <c r="M6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="7" spans="2:13">
@@ -2732,7 +2731,7 @@
         <v>3</v>
       </c>
       <c r="D7" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F7" t="s">
         <v>77</v>
@@ -2755,24 +2754,27 @@
         <v>192</v>
       </c>
       <c r="D8" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F8" t="s">
         <v>78</v>
       </c>
+      <c r="H8" t="s">
+        <v>201</v>
+      </c>
       <c r="J8" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="K8" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="M8" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="9" spans="2:13">
       <c r="B9" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D9" t="s">
         <v>197</v>
@@ -2780,11 +2782,14 @@
       <c r="F9" t="s">
         <v>79</v>
       </c>
+      <c r="H9" t="s">
+        <v>230</v>
+      </c>
       <c r="J9" t="s">
         <v>116</v>
       </c>
       <c r="K9" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="M9" t="s">
         <v>162</v>
@@ -2792,7 +2797,7 @@
     </row>
     <row r="10" spans="2:13">
       <c r="B10" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D10" t="s">
         <v>196</v>
@@ -2801,7 +2806,7 @@
         <v>205</v>
       </c>
       <c r="M10" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="11" spans="2:13">
@@ -2812,7 +2817,7 @@
         <v>206</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="M11" t="s">
         <v>90</v>
@@ -2820,10 +2825,10 @@
     </row>
     <row r="12" spans="2:13">
       <c r="B12" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="J12" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="K12" t="s">
         <v>1</v>
@@ -2894,7 +2899,7 @@
     </row>
     <row r="25" spans="2:4">
       <c r="B25" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
   </sheetData>

--- a/Documents/DBdesign.xlsx
+++ b/Documents/DBdesign.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitLab\joboffer\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F380A88C-3631-4358-AEF4-22CCBFBF3F1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A263095B-ADAD-4812-9CF8-7D5E900CF01A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" firstSheet="1" activeTab="7" xr2:uid="{BEC21941-B947-480A-A7E6-7B63159DE119}"/>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="7" xr2:uid="{BEC21941-B947-480A-A7E6-7B63159DE119}"/>
   </bookViews>
   <sheets>
     <sheet name="RBAC+ABAC" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="443" uniqueCount="231">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="447" uniqueCount="232">
   <si>
     <t>JobOfferUsers</t>
   </si>
@@ -646,12 +646,6 @@
     <t>BandId</t>
   </si>
   <si>
-    <t>Option</t>
-  </si>
-  <si>
-    <t>Current</t>
-  </si>
-  <si>
     <t>Increase</t>
   </si>
   <si>
@@ -670,9 +664,6 @@
     <t>ProposalId</t>
   </si>
   <si>
-    <t>ApproverType</t>
-  </si>
-  <si>
     <t>ApproveBy</t>
   </si>
   <si>
@@ -721,13 +712,25 @@
     <t>DueAt</t>
   </si>
   <si>
-    <t>Propose</t>
-  </si>
-  <si>
     <t>Salary</t>
   </si>
   <si>
     <t>JobPositionId</t>
+  </si>
+  <si>
+    <t>OptionNum</t>
+  </si>
+  <si>
+    <t>ProposeSalary</t>
+  </si>
+  <si>
+    <t>Escalate</t>
+  </si>
+  <si>
+    <t>ApproverTypes</t>
+  </si>
+  <si>
+    <t>ChannelId</t>
   </si>
 </sst>
 </file>
@@ -2628,10 +2631,10 @@
         <v>200</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
     </row>
     <row r="3" spans="2:13">
@@ -2659,7 +2662,7 @@
     </row>
     <row r="4" spans="2:13">
       <c r="B4" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="D4" t="s">
         <v>16</v>
@@ -2674,7 +2677,7 @@
         <v>201</v>
       </c>
       <c r="K4" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="M4" t="s">
         <v>201</v>
@@ -2682,10 +2685,10 @@
     </row>
     <row r="5" spans="2:13">
       <c r="B5" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="D5" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="F5" t="s">
         <v>187</v>
@@ -2700,15 +2703,15 @@
         <v>69</v>
       </c>
       <c r="M5" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
     </row>
     <row r="6" spans="2:13">
       <c r="B6" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="D6" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="F6" t="s">
         <v>76</v>
@@ -2717,13 +2720,13 @@
         <v>52</v>
       </c>
       <c r="J6" t="s">
-        <v>203</v>
+        <v>227</v>
       </c>
       <c r="K6" t="s">
         <v>162</v>
       </c>
       <c r="M6" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
     </row>
     <row r="7" spans="2:13">
@@ -2731,7 +2734,7 @@
         <v>3</v>
       </c>
       <c r="D7" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="F7" t="s">
         <v>77</v>
@@ -2740,13 +2743,13 @@
         <v>189</v>
       </c>
       <c r="J7" t="s">
-        <v>204</v>
+        <v>114</v>
       </c>
       <c r="K7" t="s">
         <v>125</v>
       </c>
       <c r="M7" t="s">
-        <v>167</v>
+        <v>231</v>
       </c>
     </row>
     <row r="8" spans="2:13">
@@ -2754,7 +2757,7 @@
         <v>192</v>
       </c>
       <c r="D8" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="F8" t="s">
         <v>78</v>
@@ -2766,15 +2769,15 @@
         <v>228</v>
       </c>
       <c r="K8" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="M8" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
     </row>
     <row r="9" spans="2:13">
       <c r="B9" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="D9" t="s">
         <v>197</v>
@@ -2783,13 +2786,13 @@
         <v>79</v>
       </c>
       <c r="H9" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="J9" t="s">
         <v>116</v>
       </c>
       <c r="K9" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="M9" t="s">
         <v>162</v>
@@ -2797,16 +2800,16 @@
     </row>
     <row r="10" spans="2:13">
       <c r="B10" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="D10" t="s">
         <v>196</v>
       </c>
       <c r="J10" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="M10" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
     </row>
     <row r="11" spans="2:13">
@@ -2814,10 +2817,10 @@
         <v>191</v>
       </c>
       <c r="J11" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>211</v>
+        <v>230</v>
       </c>
       <c r="M11" t="s">
         <v>90</v>
@@ -2825,10 +2828,10 @@
     </row>
     <row r="12" spans="2:13">
       <c r="B12" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="J12" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="K12" t="s">
         <v>1</v>
@@ -2841,8 +2844,24 @@
       <c r="B13" t="s">
         <v>193</v>
       </c>
+      <c r="J13" t="s">
+        <v>69</v>
+      </c>
       <c r="K13" t="s">
         <v>83</v>
+      </c>
+      <c r="M13" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="14" spans="2:13">
+      <c r="J14" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="15" spans="2:13">
+      <c r="J15" t="s">
+        <v>229</v>
       </c>
     </row>
     <row r="17" spans="2:4">
@@ -2899,7 +2918,7 @@
     </row>
     <row r="25" spans="2:4">
       <c r="B25" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
   </sheetData>

--- a/Documents/DBdesign.xlsx
+++ b/Documents/DBdesign.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitLab\joboffer\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A263095B-ADAD-4812-9CF8-7D5E900CF01A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63ABFC0C-6F04-4EAF-AF7D-CC080DCADF8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="7" xr2:uid="{BEC21941-B947-480A-A7E6-7B63159DE119}"/>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="8" xr2:uid="{BEC21941-B947-480A-A7E6-7B63159DE119}"/>
   </bookViews>
   <sheets>
     <sheet name="RBAC+ABAC" sheetId="1" r:id="rId1"/>
@@ -21,6 +21,7 @@
     <sheet name="Discussion" sheetId="6" r:id="rId6"/>
     <sheet name="WorkFlow" sheetId="8" r:id="rId7"/>
     <sheet name="ReDesign" sheetId="9" r:id="rId8"/>
+    <sheet name="Matrix" sheetId="10" r:id="rId9"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -35,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="447" uniqueCount="232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="475" uniqueCount="244">
   <si>
     <t>JobOfferUsers</t>
   </si>
@@ -731,6 +732,42 @@
   </si>
   <si>
     <t>ChannelId</t>
+  </si>
+  <si>
+    <t>GradeTypes</t>
+  </si>
+  <si>
+    <t>SalaryGrades</t>
+  </si>
+  <si>
+    <t>GradeName</t>
+  </si>
+  <si>
+    <t>CompanySalaryGrades</t>
+  </si>
+  <si>
+    <t>GradeId</t>
+  </si>
+  <si>
+    <t>SalaryBands</t>
+  </si>
+  <si>
+    <t>CSGId</t>
+  </si>
+  <si>
+    <t>Minimun</t>
+  </si>
+  <si>
+    <t>Midpoint</t>
+  </si>
+  <si>
+    <t>Maximum</t>
+  </si>
+  <si>
+    <t>EffectFrom</t>
+  </si>
+  <si>
+    <t>EffectTo</t>
   </si>
 </sst>
 </file>
@@ -2924,4 +2961,120 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F800367-D121-468C-B2BA-C9E3C3CB19BA}">
+  <dimension ref="B2:L8"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
+  <cols>
+    <col min="2" max="2" width="12.54296875" customWidth="1"/>
+    <col min="4" max="4" width="10.6328125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.453125" customWidth="1"/>
+    <col min="8" max="8" width="20.08984375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="17.54296875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:12">
+      <c r="B2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="3" spans="2:12">
+      <c r="B3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F3" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" t="s">
+        <v>1</v>
+      </c>
+      <c r="J3" t="s">
+        <v>1</v>
+      </c>
+      <c r="L3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="2:12">
+      <c r="B4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D4" t="s">
+        <v>83</v>
+      </c>
+      <c r="F4" t="s">
+        <v>125</v>
+      </c>
+      <c r="H4" t="s">
+        <v>8</v>
+      </c>
+      <c r="J4" t="s">
+        <v>8</v>
+      </c>
+      <c r="L4" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="5" spans="2:12">
+      <c r="B5" t="s">
+        <v>6</v>
+      </c>
+      <c r="F5" t="s">
+        <v>234</v>
+      </c>
+      <c r="H5" t="s">
+        <v>236</v>
+      </c>
+      <c r="J5" t="s">
+        <v>242</v>
+      </c>
+      <c r="L5" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="6" spans="2:12">
+      <c r="J6" t="s">
+        <v>243</v>
+      </c>
+      <c r="L6" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="7" spans="2:12">
+      <c r="J7" t="s">
+        <v>30</v>
+      </c>
+      <c r="L7" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="8" spans="2:12">
+      <c r="L8" t="s">
+        <v>241</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Documents/DBdesign.xlsx
+++ b/Documents/DBdesign.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitLab\joboffer\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63ABFC0C-6F04-4EAF-AF7D-CC080DCADF8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB5EC828-5E5E-41B9-B2F1-946A454227EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="8" xr2:uid="{BEC21941-B947-480A-A7E6-7B63159DE119}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" activeTab="9" xr2:uid="{BEC21941-B947-480A-A7E6-7B63159DE119}"/>
   </bookViews>
   <sheets>
     <sheet name="RBAC+ABAC" sheetId="1" r:id="rId1"/>
@@ -22,6 +22,7 @@
     <sheet name="WorkFlow" sheetId="8" r:id="rId7"/>
     <sheet name="ReDesign" sheetId="9" r:id="rId8"/>
     <sheet name="Matrix" sheetId="10" r:id="rId9"/>
+    <sheet name="Comp&amp;Ben" sheetId="11" r:id="rId10"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="475" uniqueCount="244">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="608" uniqueCount="311">
   <si>
     <t>JobOfferUsers</t>
   </si>
@@ -764,17 +765,218 @@
     <t>Maximum</t>
   </si>
   <si>
-    <t>EffectFrom</t>
-  </si>
-  <si>
-    <t>EffectTo</t>
+    <t>PlanName</t>
+  </si>
+  <si>
+    <t>AreaName</t>
+  </si>
+  <si>
+    <t>AreaId</t>
+  </si>
+  <si>
+    <t>ShiftName</t>
+  </si>
+  <si>
+    <t>ShiftId</t>
+  </si>
+  <si>
+    <t>Motorized</t>
+  </si>
+  <si>
+    <t>AllowSpec</t>
+  </si>
+  <si>
+    <t>AllowTrans</t>
+  </si>
+  <si>
+    <t>Incentive</t>
+  </si>
+  <si>
+    <t>NonSwipe</t>
+  </si>
+  <si>
+    <t>PlanId</t>
+  </si>
+  <si>
+    <t>CompBenEmpType</t>
+  </si>
+  <si>
+    <t>CompBenPlans</t>
+  </si>
+  <si>
+    <t>CompBenArea</t>
+  </si>
+  <si>
+    <t>CompBenSched</t>
+  </si>
+  <si>
+    <t>CompBenShift</t>
+  </si>
+  <si>
+    <t>CompBenFreq</t>
+  </si>
+  <si>
+    <t>FreqName</t>
+  </si>
+  <si>
+    <t>CompBenItmCat</t>
+  </si>
+  <si>
+    <t>CatName</t>
+  </si>
+  <si>
+    <t>CatId</t>
+  </si>
+  <si>
+    <t>FreqId</t>
+  </si>
+  <si>
+    <t>ItmName</t>
+  </si>
+  <si>
+    <t>ItmDesc</t>
+  </si>
+  <si>
+    <t>SchedName</t>
+  </si>
+  <si>
+    <t>SchedId</t>
+  </si>
+  <si>
+    <t>Office Based Position</t>
+  </si>
+  <si>
+    <t>Emp Status</t>
+  </si>
+  <si>
+    <t>Probationary</t>
+  </si>
+  <si>
+    <t>Work Area</t>
+  </si>
+  <si>
+    <t>Office</t>
+  </si>
+  <si>
+    <t>Shift Code</t>
+  </si>
+  <si>
+    <t>O11 - 7:30 – 17:30</t>
+  </si>
+  <si>
+    <t>Work Schedule</t>
+  </si>
+  <si>
+    <t>Compressed</t>
+  </si>
+  <si>
+    <t>Swiping Status</t>
+  </si>
+  <si>
+    <t>Swiping</t>
+  </si>
+  <si>
+    <t>Job Class</t>
+  </si>
+  <si>
+    <t>Rank &amp; File</t>
+  </si>
+  <si>
+    <t>MRI</t>
+  </si>
+  <si>
+    <t>Year</t>
+  </si>
+  <si>
+    <t>Transpo Allowance</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>Frequency</t>
+  </si>
+  <si>
+    <t>Monthly15</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Incentivized</t>
+  </si>
+  <si>
+    <t>Annual Bonus</t>
+  </si>
+  <si>
+    <t>Special Allowance</t>
+  </si>
+  <si>
+    <t>Salary Grade</t>
+  </si>
+  <si>
+    <t>SG 07*</t>
+  </si>
+  <si>
+    <t>Territory Rep, GMA</t>
+  </si>
+  <si>
+    <t>Field GMA</t>
+  </si>
+  <si>
+    <t>NPO</t>
+  </si>
+  <si>
+    <t>Non-Swiping</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No </t>
+  </si>
+  <si>
+    <t>SG 08</t>
+  </si>
+  <si>
+    <t>Project Employee - Office</t>
+  </si>
+  <si>
+    <t>Temp Project Hire</t>
+  </si>
+  <si>
+    <t>O11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NonRegular </t>
+  </si>
+  <si>
+    <t>Monthly13</t>
+  </si>
+  <si>
+    <t>NR</t>
+  </si>
+  <si>
+    <t>CompBenClass</t>
+  </si>
+  <si>
+    <t>ClassName</t>
+  </si>
+  <si>
+    <t>ClassId</t>
+  </si>
+  <si>
+    <t>CompBenMri</t>
+  </si>
+  <si>
+    <t>MriName</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -801,16 +1003,35 @@
       <color theme="1"/>
       <name val="Arial Unicode MS"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -818,17 +1039,82 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1488,6 +1774,498 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54F2E5B3-A5D7-48E1-BBB6-A4B5E81A5574}">
+  <dimension ref="B1:R33"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
+  <cols>
+    <col min="2" max="2" width="15.1796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.1796875" customWidth="1"/>
+    <col min="6" max="6" width="14.26953125" customWidth="1"/>
+    <col min="8" max="8" width="14.6328125" customWidth="1"/>
+    <col min="10" max="10" width="14.36328125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="16" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.26953125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="16" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.08984375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="16" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="15.26953125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:18" ht="15" thickBot="1"/>
+    <row r="2" spans="2:18" ht="15" thickBot="1">
+      <c r="B2" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="K2" s="6" t="s">
+        <v>268</v>
+      </c>
+      <c r="L2" s="7"/>
+      <c r="N2" s="6" t="s">
+        <v>293</v>
+      </c>
+      <c r="O2" s="7"/>
+      <c r="Q2" s="6" t="s">
+        <v>300</v>
+      </c>
+      <c r="R2" s="7"/>
+    </row>
+    <row r="3" spans="2:18" ht="15" thickBot="1">
+      <c r="B3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F3" t="s">
+        <v>1</v>
+      </c>
+      <c r="K3" s="8" t="s">
+        <v>269</v>
+      </c>
+      <c r="L3" s="5" t="s">
+        <v>270</v>
+      </c>
+      <c r="N3" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="O3" s="5" t="s">
+        <v>270</v>
+      </c>
+      <c r="Q3" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="R3" s="5" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="4" spans="2:18" ht="15" thickBot="1">
+      <c r="B4" t="s">
+        <v>242</v>
+      </c>
+      <c r="D4" t="s">
+        <v>83</v>
+      </c>
+      <c r="F4" t="s">
+        <v>252</v>
+      </c>
+      <c r="K4" s="8" t="s">
+        <v>271</v>
+      </c>
+      <c r="L4" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="N4" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="O4" s="5" t="s">
+        <v>294</v>
+      </c>
+      <c r="Q4" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="R4" s="5" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="5" spans="2:18" ht="15" thickBot="1">
+      <c r="B5" t="s">
+        <v>125</v>
+      </c>
+      <c r="F5" t="s">
+        <v>262</v>
+      </c>
+      <c r="K5" s="8" t="s">
+        <v>273</v>
+      </c>
+      <c r="L5" s="5" t="s">
+        <v>274</v>
+      </c>
+      <c r="N5" s="4" t="s">
+        <v>273</v>
+      </c>
+      <c r="O5" s="5" t="s">
+        <v>295</v>
+      </c>
+      <c r="Q5" s="4" t="s">
+        <v>273</v>
+      </c>
+      <c r="R5" s="5" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="6" spans="2:18" ht="15" thickBot="1">
+      <c r="B6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" t="s">
+        <v>263</v>
+      </c>
+      <c r="K6" s="8" t="s">
+        <v>275</v>
+      </c>
+      <c r="L6" s="5" t="s">
+        <v>276</v>
+      </c>
+      <c r="N6" s="4" t="s">
+        <v>275</v>
+      </c>
+      <c r="O6" s="5" t="s">
+        <v>276</v>
+      </c>
+      <c r="Q6" s="4" t="s">
+        <v>275</v>
+      </c>
+      <c r="R6" s="5" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="7" spans="2:18" ht="15" thickBot="1">
+      <c r="B7" t="s">
+        <v>244</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="F7" t="s">
+        <v>264</v>
+      </c>
+      <c r="K7" s="8" t="s">
+        <v>277</v>
+      </c>
+      <c r="L7" s="5" t="s">
+        <v>278</v>
+      </c>
+      <c r="N7" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="O7" s="5" t="s">
+        <v>296</v>
+      </c>
+      <c r="Q7" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="R7" s="5" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="8" spans="2:18" ht="15" thickBot="1">
+      <c r="B8" t="s">
+        <v>267</v>
+      </c>
+      <c r="D8" t="s">
+        <v>1</v>
+      </c>
+      <c r="F8" t="s">
+        <v>265</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="K8" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="L8" s="5" t="s">
+        <v>280</v>
+      </c>
+      <c r="N8" s="4" t="s">
+        <v>279</v>
+      </c>
+      <c r="O8" s="5" t="s">
+        <v>280</v>
+      </c>
+      <c r="Q8" s="4" t="s">
+        <v>279</v>
+      </c>
+      <c r="R8" s="5" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="9" spans="2:18" ht="15" thickBot="1">
+      <c r="B9" t="s">
+        <v>246</v>
+      </c>
+      <c r="D9" t="s">
+        <v>243</v>
+      </c>
+      <c r="F9" t="s">
+        <v>123</v>
+      </c>
+      <c r="H9" t="s">
+        <v>1</v>
+      </c>
+      <c r="K9" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="L9" s="5" t="s">
+        <v>282</v>
+      </c>
+      <c r="N9" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="O9" s="5" t="s">
+        <v>282</v>
+      </c>
+      <c r="Q9" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="R9" s="5" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="10" spans="2:18" ht="15" thickBot="1">
+      <c r="B10" t="s">
+        <v>247</v>
+      </c>
+      <c r="H10" t="s">
+        <v>261</v>
+      </c>
+      <c r="K10" s="8" t="s">
+        <v>283</v>
+      </c>
+      <c r="L10" s="5" t="s">
+        <v>284</v>
+      </c>
+      <c r="N10" s="4" t="s">
+        <v>283</v>
+      </c>
+      <c r="O10" s="5" t="s">
+        <v>297</v>
+      </c>
+      <c r="Q10" s="4" t="s">
+        <v>283</v>
+      </c>
+      <c r="R10" s="5" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="11" spans="2:18" ht="15" thickBot="1">
+      <c r="B11" t="s">
+        <v>249</v>
+      </c>
+      <c r="K11" s="8" t="s">
+        <v>285</v>
+      </c>
+      <c r="L11" s="5" t="s">
+        <v>286</v>
+      </c>
+      <c r="N11" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="O11" s="5" t="s">
+        <v>286</v>
+      </c>
+      <c r="Q11" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="R11" s="5" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="12" spans="2:18" ht="15" thickBot="1">
+      <c r="B12" t="s">
+        <v>248</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="K12" s="8" t="s">
+        <v>247</v>
+      </c>
+      <c r="L12" s="5" t="s">
+        <v>287</v>
+      </c>
+      <c r="N12" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="O12" s="5" t="s">
+        <v>284</v>
+      </c>
+      <c r="Q12" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="R12" s="5" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="13" spans="2:18" ht="15" thickBot="1">
+      <c r="B13" t="s">
+        <v>250</v>
+      </c>
+      <c r="D13" t="s">
+        <v>1</v>
+      </c>
+      <c r="K13" s="8" t="s">
+        <v>288</v>
+      </c>
+      <c r="L13" s="5" t="s">
+        <v>287</v>
+      </c>
+      <c r="N13" s="4" t="s">
+        <v>288</v>
+      </c>
+      <c r="O13" s="5" t="s">
+        <v>284</v>
+      </c>
+      <c r="Q13" s="4" t="s">
+        <v>288</v>
+      </c>
+      <c r="R13" s="5" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="14" spans="2:18" ht="15" thickBot="1">
+      <c r="B14" t="s">
+        <v>204</v>
+      </c>
+      <c r="D14" t="s">
+        <v>266</v>
+      </c>
+      <c r="K14" s="8" t="s">
+        <v>289</v>
+      </c>
+      <c r="L14" s="5" t="s">
+        <v>287</v>
+      </c>
+      <c r="N14" s="4" t="s">
+        <v>289</v>
+      </c>
+      <c r="O14" s="5" t="s">
+        <v>298</v>
+      </c>
+      <c r="Q14" s="4" t="s">
+        <v>289</v>
+      </c>
+      <c r="R14" s="5" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="15" spans="2:18" ht="15" thickBot="1">
+      <c r="B15" t="s">
+        <v>251</v>
+      </c>
+      <c r="K15" s="8" t="s">
+        <v>290</v>
+      </c>
+      <c r="L15" s="5" t="s">
+        <v>287</v>
+      </c>
+      <c r="N15" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="O15" s="5" t="s">
+        <v>287</v>
+      </c>
+      <c r="Q15" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="R15" s="5" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="16" spans="2:18" ht="15" thickBot="1">
+      <c r="B16" t="s">
+        <v>308</v>
+      </c>
+      <c r="K16" s="8" t="s">
+        <v>291</v>
+      </c>
+      <c r="L16" s="5" t="s">
+        <v>292</v>
+      </c>
+      <c r="N16" s="4" t="s">
+        <v>291</v>
+      </c>
+      <c r="O16" s="5" t="s">
+        <v>299</v>
+      </c>
+      <c r="Q16" s="4" t="s">
+        <v>291</v>
+      </c>
+      <c r="R16" s="5" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="17" spans="2:4">
+      <c r="B17" t="s">
+        <v>238</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="18" spans="2:4">
+      <c r="D18" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="2:4">
+      <c r="D19" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="22" spans="2:4">
+      <c r="D22" s="1" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="23" spans="2:4">
+      <c r="D23" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="2:4">
+      <c r="D24" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="26" spans="2:4">
+      <c r="D26" s="1" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="27" spans="2:4">
+      <c r="D27" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="2:4">
+      <c r="D28" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="31" spans="2:4">
+      <c r="D31" s="1" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="32" spans="2:4">
+      <c r="D32" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="4:4">
+      <c r="D33" t="s">
+        <v>310</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="N2:O2"/>
+    <mergeCell ref="Q2:R2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{026B99F0-FC57-47AB-AF03-F4ABCCD02BF2}">
   <dimension ref="B2:H16"/>
@@ -3047,24 +3825,18 @@
         <v>236</v>
       </c>
       <c r="J5" t="s">
-        <v>242</v>
+        <v>30</v>
       </c>
       <c r="L5" t="s">
         <v>238</v>
       </c>
     </row>
     <row r="6" spans="2:12">
-      <c r="J6" t="s">
-        <v>243</v>
-      </c>
       <c r="L6" t="s">
         <v>239</v>
       </c>
     </row>
     <row r="7" spans="2:12">
-      <c r="J7" t="s">
-        <v>30</v>
-      </c>
       <c r="L7" t="s">
         <v>240</v>
       </c>

--- a/Documents/DBdesign.xlsx
+++ b/Documents/DBdesign.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitLab\joboffer\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB5EC828-5E5E-41B9-B2F1-946A454227EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A317693D-7169-4E67-902E-1930A0B022A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" activeTab="9" xr2:uid="{BEC21941-B947-480A-A7E6-7B63159DE119}"/>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="9" xr2:uid="{BEC21941-B947-480A-A7E6-7B63159DE119}"/>
   </bookViews>
   <sheets>
     <sheet name="RBAC+ABAC" sheetId="1" r:id="rId1"/>
@@ -24,10 +24,21 @@
     <sheet name="Matrix" sheetId="10" r:id="rId9"/>
     <sheet name="Comp&amp;Ben" sheetId="11" r:id="rId10"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="2"/>
@@ -37,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="608" uniqueCount="311">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="612" uniqueCount="310">
   <si>
     <t>JobOfferUsers</t>
   </si>
@@ -826,9 +837,6 @@
   </si>
   <si>
     <t>CatId</t>
-  </si>
-  <si>
-    <t>FreqId</t>
   </si>
   <si>
     <t>ItmName</t>
@@ -1017,7 +1025,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1027,6 +1035,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1093,7 +1107,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1108,13 +1122,16 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1779,7 +1796,7 @@
   <dimension ref="B1:R33"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="15.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.6328125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="17.1796875" customWidth="1"/>
     <col min="6" max="6" width="14.26953125" customWidth="1"/>
     <col min="8" max="8" width="14.6328125" customWidth="1"/>
@@ -1803,18 +1820,21 @@
       <c r="F2" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="K2" s="6" t="s">
-        <v>268</v>
-      </c>
-      <c r="L2" s="7"/>
-      <c r="N2" s="6" t="s">
-        <v>293</v>
-      </c>
-      <c r="O2" s="7"/>
-      <c r="Q2" s="6" t="s">
-        <v>300</v>
-      </c>
-      <c r="R2" s="7"/>
+      <c r="H2" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="K2" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="L2" s="8"/>
+      <c r="N2" s="7" t="s">
+        <v>292</v>
+      </c>
+      <c r="O2" s="8"/>
+      <c r="Q2" s="7" t="s">
+        <v>299</v>
+      </c>
+      <c r="R2" s="8"/>
     </row>
     <row r="3" spans="2:18" ht="15" thickBot="1">
       <c r="B3" t="s">
@@ -1826,23 +1846,26 @@
       <c r="F3" t="s">
         <v>1</v>
       </c>
-      <c r="K3" s="8" t="s">
+      <c r="H3" t="s">
+        <v>1</v>
+      </c>
+      <c r="K3" s="6" t="s">
+        <v>268</v>
+      </c>
+      <c r="L3" s="5" t="s">
         <v>269</v>
       </c>
-      <c r="L3" s="5" t="s">
-        <v>270</v>
-      </c>
       <c r="N3" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="O3" s="5" t="s">
         <v>269</v>
       </c>
-      <c r="O3" s="5" t="s">
-        <v>270</v>
-      </c>
       <c r="Q3" s="4" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="R3" s="5" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="4" spans="2:18" ht="15" thickBot="1">
@@ -1855,23 +1878,26 @@
       <c r="F4" t="s">
         <v>252</v>
       </c>
-      <c r="K4" s="8" t="s">
+      <c r="H4" t="s">
+        <v>261</v>
+      </c>
+      <c r="K4" s="6" t="s">
+        <v>270</v>
+      </c>
+      <c r="L4" s="5" t="s">
         <v>271</v>
       </c>
-      <c r="L4" s="5" t="s">
-        <v>272</v>
-      </c>
       <c r="N4" s="4" t="s">
+        <v>270</v>
+      </c>
+      <c r="O4" s="5" t="s">
+        <v>293</v>
+      </c>
+      <c r="Q4" s="4" t="s">
+        <v>270</v>
+      </c>
+      <c r="R4" s="5" t="s">
         <v>271</v>
-      </c>
-      <c r="O4" s="5" t="s">
-        <v>294</v>
-      </c>
-      <c r="Q4" s="4" t="s">
-        <v>271</v>
-      </c>
-      <c r="R4" s="5" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="5" spans="2:18" ht="15" thickBot="1">
@@ -1881,23 +1907,23 @@
       <c r="F5" t="s">
         <v>262</v>
       </c>
-      <c r="K5" s="8" t="s">
+      <c r="K5" s="9" t="s">
+        <v>272</v>
+      </c>
+      <c r="L5" s="5" t="s">
         <v>273</v>
       </c>
-      <c r="L5" s="5" t="s">
-        <v>274</v>
-      </c>
       <c r="N5" s="4" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="O5" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="Q5" s="4" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="R5" s="5" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="6" spans="2:18" ht="15" thickBot="1">
@@ -1907,23 +1933,23 @@
       <c r="F6" t="s">
         <v>263</v>
       </c>
-      <c r="K6" s="8" t="s">
+      <c r="K6" s="6" t="s">
+        <v>274</v>
+      </c>
+      <c r="L6" s="5" t="s">
         <v>275</v>
       </c>
-      <c r="L6" s="5" t="s">
-        <v>276</v>
-      </c>
       <c r="N6" s="4" t="s">
+        <v>274</v>
+      </c>
+      <c r="O6" s="5" t="s">
         <v>275</v>
       </c>
-      <c r="O6" s="5" t="s">
-        <v>276</v>
-      </c>
       <c r="Q6" s="4" t="s">
+        <v>274</v>
+      </c>
+      <c r="R6" s="5" t="s">
         <v>275</v>
-      </c>
-      <c r="R6" s="5" t="s">
-        <v>276</v>
       </c>
     </row>
     <row r="7" spans="2:18" ht="15" thickBot="1">
@@ -1936,55 +1962,52 @@
       <c r="F7" t="s">
         <v>264</v>
       </c>
-      <c r="K7" s="8" t="s">
+      <c r="K7" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="L7" s="5" t="s">
         <v>277</v>
       </c>
-      <c r="L7" s="5" t="s">
-        <v>278</v>
-      </c>
       <c r="N7" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="O7" s="5" t="s">
+        <v>295</v>
+      </c>
+      <c r="Q7" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="R7" s="5" t="s">
         <v>277</v>
-      </c>
-      <c r="O7" s="5" t="s">
-        <v>296</v>
-      </c>
-      <c r="Q7" s="4" t="s">
-        <v>277</v>
-      </c>
-      <c r="R7" s="5" t="s">
-        <v>278</v>
       </c>
     </row>
     <row r="8" spans="2:18" ht="15" thickBot="1">
       <c r="B8" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D8" t="s">
         <v>1</v>
       </c>
       <c r="F8" t="s">
-        <v>265</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="K8" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="K8" s="6" t="s">
+        <v>278</v>
+      </c>
+      <c r="L8" s="5" t="s">
         <v>279</v>
       </c>
-      <c r="L8" s="5" t="s">
-        <v>280</v>
-      </c>
       <c r="N8" s="4" t="s">
+        <v>278</v>
+      </c>
+      <c r="O8" s="5" t="s">
         <v>279</v>
       </c>
-      <c r="O8" s="5" t="s">
-        <v>280</v>
-      </c>
       <c r="Q8" s="4" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="R8" s="5" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="9" spans="2:18" ht="15" thickBot="1">
@@ -1995,77 +2018,71 @@
         <v>243</v>
       </c>
       <c r="F9" t="s">
-        <v>123</v>
-      </c>
-      <c r="H9" t="s">
-        <v>1</v>
-      </c>
-      <c r="K9" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="K9" s="6" t="s">
+        <v>280</v>
+      </c>
+      <c r="L9" s="5" t="s">
         <v>281</v>
       </c>
-      <c r="L9" s="5" t="s">
-        <v>282</v>
-      </c>
       <c r="N9" s="4" t="s">
+        <v>280</v>
+      </c>
+      <c r="O9" s="5" t="s">
         <v>281</v>
       </c>
-      <c r="O9" s="5" t="s">
-        <v>282</v>
-      </c>
       <c r="Q9" s="4" t="s">
+        <v>280</v>
+      </c>
+      <c r="R9" s="5" t="s">
         <v>281</v>
-      </c>
-      <c r="R9" s="5" t="s">
-        <v>282</v>
       </c>
     </row>
     <row r="10" spans="2:18" ht="15" thickBot="1">
       <c r="B10" t="s">
         <v>247</v>
       </c>
-      <c r="H10" t="s">
-        <v>261</v>
-      </c>
-      <c r="K10" s="8" t="s">
+      <c r="K10" s="6" t="s">
+        <v>282</v>
+      </c>
+      <c r="L10" s="5" t="s">
         <v>283</v>
       </c>
-      <c r="L10" s="5" t="s">
-        <v>284</v>
-      </c>
       <c r="N10" s="4" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="O10" s="5" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="Q10" s="4" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="R10" s="5" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="11" spans="2:18" ht="15" thickBot="1">
       <c r="B11" t="s">
         <v>249</v>
       </c>
-      <c r="K11" s="8" t="s">
+      <c r="K11" s="6" t="s">
+        <v>284</v>
+      </c>
+      <c r="L11" s="5" t="s">
         <v>285</v>
       </c>
-      <c r="L11" s="5" t="s">
-        <v>286</v>
-      </c>
       <c r="N11" s="4" t="s">
+        <v>284</v>
+      </c>
+      <c r="O11" s="5" t="s">
         <v>285</v>
       </c>
-      <c r="O11" s="5" t="s">
-        <v>286</v>
-      </c>
       <c r="Q11" s="4" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="R11" s="5" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="12" spans="2:18" ht="15" thickBot="1">
@@ -2075,23 +2092,23 @@
       <c r="D12" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="K12" s="8" t="s">
+      <c r="K12" s="6" t="s">
         <v>247</v>
       </c>
       <c r="L12" s="5" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="N12" s="4" t="s">
         <v>247</v>
       </c>
       <c r="O12" s="5" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="Q12" s="4" t="s">
         <v>247</v>
       </c>
       <c r="R12" s="5" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="13" spans="2:18" ht="15" thickBot="1">
@@ -2101,23 +2118,23 @@
       <c r="D13" t="s">
         <v>1</v>
       </c>
-      <c r="K13" s="8" t="s">
-        <v>288</v>
+      <c r="K13" s="6" t="s">
+        <v>287</v>
       </c>
       <c r="L13" s="5" t="s">
+        <v>286</v>
+      </c>
+      <c r="N13" s="4" t="s">
         <v>287</v>
       </c>
-      <c r="N13" s="4" t="s">
-        <v>288</v>
-      </c>
       <c r="O13" s="5" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="Q13" s="4" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="R13" s="5" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="14" spans="2:18" ht="15" thickBot="1">
@@ -2125,71 +2142,71 @@
         <v>204</v>
       </c>
       <c r="D14" t="s">
-        <v>266</v>
-      </c>
-      <c r="K14" s="8" t="s">
-        <v>289</v>
+        <v>265</v>
+      </c>
+      <c r="K14" s="6" t="s">
+        <v>288</v>
       </c>
       <c r="L14" s="5" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="N14" s="4" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="O14" s="5" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="Q14" s="4" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="R14" s="5" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="15" spans="2:18" ht="15" thickBot="1">
       <c r="B15" t="s">
         <v>251</v>
       </c>
-      <c r="K15" s="8" t="s">
-        <v>290</v>
+      <c r="K15" s="6" t="s">
+        <v>289</v>
       </c>
       <c r="L15" s="5" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="N15" s="4" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="O15" s="5" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="Q15" s="4" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="R15" s="5" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="16" spans="2:18" ht="15" thickBot="1">
       <c r="B16" t="s">
-        <v>308</v>
-      </c>
-      <c r="K16" s="8" t="s">
+        <v>307</v>
+      </c>
+      <c r="K16" s="6" t="s">
+        <v>290</v>
+      </c>
+      <c r="L16" s="5" t="s">
         <v>291</v>
       </c>
-      <c r="L16" s="5" t="s">
-        <v>292</v>
-      </c>
       <c r="N16" s="4" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="O16" s="5" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="Q16" s="4" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="R16" s="5" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="17" spans="2:4">
@@ -2210,19 +2227,35 @@
         <v>245</v>
       </c>
     </row>
+    <row r="20" spans="2:4">
+      <c r="B20" s="1" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="21" spans="2:4">
+      <c r="B21" t="s">
+        <v>1</v>
+      </c>
+    </row>
     <row r="22" spans="2:4">
+      <c r="B22" t="s">
+        <v>252</v>
+      </c>
       <c r="D22" s="1" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="23" spans="2:4">
+      <c r="B23" t="s">
+        <v>8</v>
+      </c>
       <c r="D23" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="24" spans="2:4">
       <c r="D24" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="26" spans="2:4">
@@ -2242,7 +2275,7 @@
     </row>
     <row r="31" spans="2:4">
       <c r="D31" s="1" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="32" spans="2:4">
@@ -2252,7 +2285,7 @@
     </row>
     <row r="33" spans="4:4">
       <c r="D33" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
   </sheetData>

--- a/Documents/DBdesign.xlsx
+++ b/Documents/DBdesign.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitLab\joboffer\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Gitlab\joboffer\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A317693D-7169-4E67-902E-1930A0B022A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8909E14-0854-40A6-A01B-BE86E746EE8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="9" xr2:uid="{BEC21941-B947-480A-A7E6-7B63159DE119}"/>
+    <workbookView xWindow="2856" yWindow="2964" windowWidth="23040" windowHeight="12168" firstSheet="3" activeTab="9" xr2:uid="{BEC21941-B947-480A-A7E6-7B63159DE119}"/>
   </bookViews>
   <sheets>
     <sheet name="RBAC+ABAC" sheetId="1" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="612" uniqueCount="310">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="636" uniqueCount="319">
   <si>
     <t>JobOfferUsers</t>
   </si>
@@ -978,13 +978,40 @@
   </si>
   <si>
     <t>MriName</t>
+  </si>
+  <si>
+    <t>SGId</t>
+  </si>
+  <si>
+    <t>PckgName</t>
+  </si>
+  <si>
+    <t>CompId</t>
+  </si>
+  <si>
+    <t>CompBenPckgs</t>
+  </si>
+  <si>
+    <t>CompBenPckgItms</t>
+  </si>
+  <si>
+    <t>PckgId</t>
+  </si>
+  <si>
+    <t>ItemId</t>
+  </si>
+  <si>
+    <t>CBPlnHasItem</t>
+  </si>
+  <si>
+    <t>CBPckHasItem</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1125,14 +1152,14 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1469,16 +1496,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9EF47D5C-035D-491F-B6E5-626F15CDCBDA}">
   <dimension ref="B2:J51"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="16.54296875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.90625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.08984375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.54296875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="16.6328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19.44140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:10">
+    <row r="2" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1495,7 +1522,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="3" spans="2:10">
+    <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>1</v>
       </c>
@@ -1512,7 +1539,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="2:10">
+    <row r="4" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
         <v>47</v>
       </c>
@@ -1529,7 +1556,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="2:10">
+    <row r="5" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
         <v>2</v>
       </c>
@@ -1546,7 +1573,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="6" spans="2:10">
+    <row r="6" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
         <v>3</v>
       </c>
@@ -1560,7 +1587,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="9" spans="2:10">
+    <row r="9" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B9" s="1" t="s">
         <v>4</v>
       </c>
@@ -1571,7 +1598,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="2:10">
+    <row r="10" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
         <v>1</v>
       </c>
@@ -1582,7 +1609,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="2:10">
+    <row r="11" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
         <v>5</v>
       </c>
@@ -1593,7 +1620,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="12" spans="2:10">
+    <row r="12" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
         <v>6</v>
       </c>
@@ -1604,7 +1631,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="2:10">
+    <row r="13" spans="2:10" x14ac:dyDescent="0.3">
       <c r="D13" t="s">
         <v>10</v>
       </c>
@@ -1612,32 +1639,32 @@
         <v>17</v>
       </c>
     </row>
-    <row r="14" spans="2:10">
+    <row r="14" spans="2:10" x14ac:dyDescent="0.3">
       <c r="F14" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="15" spans="2:10">
+    <row r="15" spans="2:10" x14ac:dyDescent="0.3">
       <c r="F15" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="16" spans="2:10">
+    <row r="16" spans="2:10" x14ac:dyDescent="0.3">
       <c r="F16" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="2:6">
+    <row r="17" spans="2:6" x14ac:dyDescent="0.3">
       <c r="F17" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="18" spans="2:6">
+    <row r="18" spans="2:6" x14ac:dyDescent="0.3">
       <c r="F18" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="21" spans="2:6">
+    <row r="21" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B21" s="1" t="s">
         <v>22</v>
       </c>
@@ -1648,7 +1675,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="22" spans="2:6">
+    <row r="22" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B22" t="s">
         <v>1</v>
       </c>
@@ -1659,7 +1686,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="2:6">
+    <row r="23" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B23" t="s">
         <v>23</v>
       </c>
@@ -1670,7 +1697,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="24" spans="2:6">
+    <row r="24" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B24" t="s">
         <v>24</v>
       </c>
@@ -1681,107 +1708,107 @@
         <v>26</v>
       </c>
     </row>
-    <row r="25" spans="2:6">
+    <row r="25" spans="2:6" x14ac:dyDescent="0.3">
       <c r="F25" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="2:6">
+    <row r="26" spans="2:6" x14ac:dyDescent="0.3">
       <c r="F26" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="27" spans="2:6">
+    <row r="27" spans="2:6" x14ac:dyDescent="0.3">
       <c r="F27" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="30" spans="2:6">
+    <row r="30" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B30" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="31" spans="2:6">
+    <row r="31" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B31" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="2:6">
+    <row r="32" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B32" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="33" spans="2:2">
+    <row r="33" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B33" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="34" spans="2:2">
+    <row r="34" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B34" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="37" spans="2:2">
+    <row r="37" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B37" s="1" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="38" spans="2:2">
+    <row r="38" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B38" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="2:2">
+    <row r="39" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B39" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="40" spans="2:2">
+    <row r="40" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B40" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="41" spans="2:2">
+    <row r="41" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B41" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="42" spans="2:2">
+    <row r="42" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B42" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="43" spans="2:2">
+    <row r="43" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B43" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="44" spans="2:2">
+    <row r="44" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B44" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="45" spans="2:2">
+    <row r="45" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B45" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="48" spans="2:2">
+    <row r="48" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B48" s="1" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="49" spans="2:2">
+    <row r="49" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B49" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="2:2">
+    <row r="50" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B50" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="51" spans="2:2">
+    <row r="51" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B51" t="s">
         <v>50</v>
       </c>
@@ -1793,24 +1820,24 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54F2E5B3-A5D7-48E1-BBB6-A4B5E81A5574}">
-  <dimension ref="B1:R33"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <dimension ref="B1:R35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="16.6328125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.1796875" customWidth="1"/>
-    <col min="6" max="6" width="14.26953125" customWidth="1"/>
-    <col min="8" max="8" width="14.6328125" customWidth="1"/>
-    <col min="10" max="10" width="14.36328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.109375" customWidth="1"/>
+    <col min="6" max="6" width="19.44140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.6640625" customWidth="1"/>
+    <col min="10" max="10" width="14.33203125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="16" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15.26953125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.21875" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="16" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="11.08984375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.109375" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="16" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="15.26953125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="15.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:18" ht="15" thickBot="1"/>
-    <row r="2" spans="2:18" ht="15" thickBot="1">
+    <row r="1" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="2" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B2" s="1" t="s">
         <v>254</v>
       </c>
@@ -1823,20 +1850,20 @@
       <c r="H2" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="K2" s="7" t="s">
+      <c r="K2" s="8" t="s">
         <v>267</v>
       </c>
-      <c r="L2" s="8"/>
-      <c r="N2" s="7" t="s">
+      <c r="L2" s="9"/>
+      <c r="N2" s="8" t="s">
         <v>292</v>
       </c>
-      <c r="O2" s="8"/>
-      <c r="Q2" s="7" t="s">
+      <c r="O2" s="9"/>
+      <c r="Q2" s="8" t="s">
         <v>299</v>
       </c>
-      <c r="R2" s="8"/>
-    </row>
-    <row r="3" spans="2:18" ht="15" thickBot="1">
+      <c r="R2" s="9"/>
+    </row>
+    <row r="3" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B3" t="s">
         <v>1</v>
       </c>
@@ -1868,7 +1895,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="4" spans="2:18" ht="15" thickBot="1">
+    <row r="4" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B4" t="s">
         <v>242</v>
       </c>
@@ -1876,7 +1903,7 @@
         <v>83</v>
       </c>
       <c r="F4" t="s">
-        <v>252</v>
+        <v>262</v>
       </c>
       <c r="H4" t="s">
         <v>261</v>
@@ -1900,14 +1927,14 @@
         <v>271</v>
       </c>
     </row>
-    <row r="5" spans="2:18" ht="15" thickBot="1">
+    <row r="5" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B5" t="s">
         <v>125</v>
       </c>
       <c r="F5" t="s">
-        <v>262</v>
-      </c>
-      <c r="K5" s="9" t="s">
+        <v>263</v>
+      </c>
+      <c r="K5" s="7" t="s">
         <v>272</v>
       </c>
       <c r="L5" s="5" t="s">
@@ -1926,12 +1953,12 @@
         <v>301</v>
       </c>
     </row>
-    <row r="6" spans="2:18" ht="15" thickBot="1">
+    <row r="6" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B6" t="s">
-        <v>8</v>
+        <v>310</v>
       </c>
       <c r="F6" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="K6" s="6" t="s">
         <v>274</v>
@@ -1952,7 +1979,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="7" spans="2:18" ht="15" thickBot="1">
+    <row r="7" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B7" t="s">
         <v>244</v>
       </c>
@@ -1960,7 +1987,7 @@
         <v>255</v>
       </c>
       <c r="F7" t="s">
-        <v>264</v>
+        <v>123</v>
       </c>
       <c r="K7" s="6" t="s">
         <v>276</v>
@@ -1981,16 +2008,13 @@
         <v>277</v>
       </c>
     </row>
-    <row r="8" spans="2:18" ht="15" thickBot="1">
+    <row r="8" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B8" t="s">
         <v>266</v>
       </c>
       <c r="D8" t="s">
         <v>1</v>
       </c>
-      <c r="F8" t="s">
-        <v>123</v>
-      </c>
       <c r="K8" s="6" t="s">
         <v>278</v>
       </c>
@@ -2010,16 +2034,13 @@
         <v>302</v>
       </c>
     </row>
-    <row r="9" spans="2:18" ht="15" thickBot="1">
+    <row r="9" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B9" t="s">
         <v>246</v>
       </c>
       <c r="D9" t="s">
         <v>243</v>
       </c>
-      <c r="F9" t="s">
-        <v>133</v>
-      </c>
       <c r="K9" s="6" t="s">
         <v>280</v>
       </c>
@@ -2039,10 +2060,13 @@
         <v>281</v>
       </c>
     </row>
-    <row r="10" spans="2:18" ht="15" thickBot="1">
+    <row r="10" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B10" t="s">
         <v>247</v>
       </c>
+      <c r="F10" s="1" t="s">
+        <v>314</v>
+      </c>
       <c r="K10" s="6" t="s">
         <v>282</v>
       </c>
@@ -2062,10 +2086,13 @@
         <v>296</v>
       </c>
     </row>
-    <row r="11" spans="2:18" ht="15" thickBot="1">
+    <row r="11" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B11" t="s">
         <v>249</v>
       </c>
+      <c r="F11" t="s">
+        <v>1</v>
+      </c>
       <c r="K11" s="6" t="s">
         <v>284</v>
       </c>
@@ -2085,13 +2112,16 @@
         <v>303</v>
       </c>
     </row>
-    <row r="12" spans="2:18" ht="15" thickBot="1">
+    <row r="12" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B12" t="s">
         <v>248</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>256</v>
       </c>
+      <c r="F12" t="s">
+        <v>315</v>
+      </c>
       <c r="K12" s="6" t="s">
         <v>247</v>
       </c>
@@ -2111,13 +2141,16 @@
         <v>286</v>
       </c>
     </row>
-    <row r="13" spans="2:18" ht="15" thickBot="1">
+    <row r="13" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B13" t="s">
         <v>250</v>
       </c>
       <c r="D13" t="s">
         <v>1</v>
       </c>
+      <c r="F13" t="s">
+        <v>262</v>
+      </c>
       <c r="K13" s="6" t="s">
         <v>287</v>
       </c>
@@ -2137,13 +2170,16 @@
         <v>286</v>
       </c>
     </row>
-    <row r="14" spans="2:18" ht="15" thickBot="1">
+    <row r="14" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B14" t="s">
         <v>204</v>
       </c>
       <c r="D14" t="s">
         <v>265</v>
       </c>
+      <c r="F14" t="s">
+        <v>263</v>
+      </c>
       <c r="K14" s="6" t="s">
         <v>288</v>
       </c>
@@ -2163,10 +2199,13 @@
         <v>297</v>
       </c>
     </row>
-    <row r="15" spans="2:18" ht="15" thickBot="1">
+    <row r="15" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B15" t="s">
         <v>251</v>
       </c>
+      <c r="F15" t="s">
+        <v>264</v>
+      </c>
       <c r="K15" s="6" t="s">
         <v>289</v>
       </c>
@@ -2186,10 +2225,13 @@
         <v>286</v>
       </c>
     </row>
-    <row r="16" spans="2:18" ht="15" thickBot="1">
+    <row r="16" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B16" t="s">
         <v>307</v>
       </c>
+      <c r="F16" t="s">
+        <v>123</v>
+      </c>
       <c r="K16" s="6" t="s">
         <v>290</v>
       </c>
@@ -2209,83 +2251,150 @@
         <v>304</v>
       </c>
     </row>
-    <row r="17" spans="2:4">
-      <c r="B17" t="s">
-        <v>238</v>
-      </c>
+    <row r="17" spans="2:6" x14ac:dyDescent="0.3">
       <c r="D17" s="1" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="18" spans="2:4">
+    <row r="18" spans="2:6" x14ac:dyDescent="0.3">
       <c r="D18" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="19" spans="2:4">
+      <c r="F18" s="1" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="19" spans="2:6" x14ac:dyDescent="0.3">
       <c r="D19" t="s">
         <v>245</v>
       </c>
-    </row>
-    <row r="20" spans="2:4">
+      <c r="F19" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B20" s="1" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="21" spans="2:4">
+        <v>313</v>
+      </c>
+      <c r="F20" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="21" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B21" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="22" spans="2:4">
+      <c r="F21" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="22" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B22" t="s">
-        <v>252</v>
+        <v>311</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>305</v>
       </c>
     </row>
-    <row r="23" spans="2:4">
+    <row r="23" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B23" t="s">
-        <v>8</v>
+        <v>312</v>
       </c>
       <c r="D23" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="2:4">
+    <row r="24" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B24" t="s">
+        <v>125</v>
+      </c>
       <c r="D24" t="s">
         <v>306</v>
       </c>
-    </row>
-    <row r="26" spans="2:4">
+      <c r="F24" s="1" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="25" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B25" t="s">
+        <v>310</v>
+      </c>
+      <c r="F25" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B26" t="s">
+        <v>244</v>
+      </c>
       <c r="D26" s="1" t="s">
         <v>258</v>
       </c>
-    </row>
-    <row r="27" spans="2:4">
+      <c r="F26" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="27" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B27" t="s">
+        <v>266</v>
+      </c>
       <c r="D27" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="28" spans="2:4">
+      <c r="F27" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="28" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B28" t="s">
+        <v>246</v>
+      </c>
       <c r="D28" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="31" spans="2:4">
+    <row r="29" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B29" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="30" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B30" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="31" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B31" t="s">
+        <v>248</v>
+      </c>
       <c r="D31" s="1" t="s">
         <v>308</v>
       </c>
     </row>
-    <row r="32" spans="2:4">
+    <row r="32" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B32" t="s">
+        <v>250</v>
+      </c>
       <c r="D32" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="4:4">
+    <row r="33" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B33" t="s">
+        <v>204</v>
+      </c>
       <c r="D33" t="s">
         <v>309</v>
+      </c>
+    </row>
+    <row r="34" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B34" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="35" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B35" t="s">
+        <v>307</v>
       </c>
     </row>
   </sheetData>
@@ -2302,14 +2411,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{026B99F0-FC57-47AB-AF03-F4ABCCD02BF2}">
   <dimension ref="B2:H16"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="22.54296875" customWidth="1"/>
-    <col min="4" max="4" width="24.453125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.44140625" customWidth="1"/>
+    <col min="4" max="4" width="24.44140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8">
+    <row r="2" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B2" s="1" t="s">
         <v>53</v>
       </c>
@@ -2323,7 +2432,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="3" spans="2:8">
+    <row r="3" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>1</v>
       </c>
@@ -2337,7 +2446,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="2:8">
+    <row r="4" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
         <v>54</v>
       </c>
@@ -2351,7 +2460,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="5" spans="2:8">
+    <row r="5" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
         <v>55</v>
       </c>
@@ -2362,7 +2471,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="6" spans="2:8">
+    <row r="6" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
         <v>56</v>
       </c>
@@ -2373,7 +2482,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="7" spans="2:8">
+    <row r="7" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
         <v>3</v>
       </c>
@@ -2384,7 +2493,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="8" spans="2:8">
+    <row r="8" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
         <v>57</v>
       </c>
@@ -2395,7 +2504,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="9" spans="2:8">
+    <row r="9" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
         <v>58</v>
       </c>
@@ -2406,7 +2515,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="10" spans="2:8">
+    <row r="10" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
         <v>59</v>
       </c>
@@ -2417,7 +2526,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="11" spans="2:8">
+    <row r="11" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
         <v>60</v>
       </c>
@@ -2428,7 +2537,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="12" spans="2:8">
+    <row r="12" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
         <v>61</v>
       </c>
@@ -2436,22 +2545,22 @@
         <v>73</v>
       </c>
     </row>
-    <row r="13" spans="2:8">
+    <row r="13" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="14" spans="2:8">
+    <row r="14" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="15" spans="2:8">
+    <row r="15" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="16" spans="2:8">
+    <row r="16" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B16" t="s">
         <v>64</v>
       </c>
@@ -2464,16 +2573,16 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9AD6FEA5-0945-4178-A2F8-A72772503D4A}">
   <dimension ref="B2:J18"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="23.7265625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.77734375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.109375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="14" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.6328125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="19.90625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="19.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:10">
+    <row r="2" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B2" s="1" t="s">
         <v>66</v>
       </c>
@@ -2490,7 +2599,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="3" spans="2:10">
+    <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>1</v>
       </c>
@@ -2507,7 +2616,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="2:10">
+    <row r="4" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
         <v>16</v>
       </c>
@@ -2524,7 +2633,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="5" spans="2:10">
+    <row r="5" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
         <v>74</v>
       </c>
@@ -2541,7 +2650,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="6" spans="2:10">
+    <row r="6" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
         <v>109</v>
       </c>
@@ -2555,7 +2664,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="7" spans="2:10">
+    <row r="7" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
         <v>110</v>
       </c>
@@ -2563,7 +2672,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="8" spans="2:10">
+    <row r="8" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
         <v>92</v>
       </c>
@@ -2571,7 +2680,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="9" spans="2:10">
+    <row r="9" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
         <v>75</v>
       </c>
@@ -2579,7 +2688,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="10" spans="2:10">
+    <row r="10" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
         <v>89</v>
       </c>
@@ -2587,7 +2696,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="11" spans="2:10">
+    <row r="11" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
         <v>90</v>
       </c>
@@ -2595,17 +2704,17 @@
         <v>100</v>
       </c>
     </row>
-    <row r="12" spans="2:10">
+    <row r="12" spans="2:10" x14ac:dyDescent="0.3">
       <c r="H12" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="13" spans="2:10">
+    <row r="13" spans="2:10" x14ac:dyDescent="0.3">
       <c r="H13" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="14" spans="2:10">
+    <row r="14" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B14" s="1" t="s">
         <v>184</v>
       </c>
@@ -2613,7 +2722,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="15" spans="2:10">
+    <row r="15" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
         <v>1</v>
       </c>
@@ -2621,7 +2730,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="16" spans="2:10">
+    <row r="16" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B16" t="s">
         <v>156</v>
       </c>
@@ -2629,12 +2738,12 @@
         <v>89</v>
       </c>
     </row>
-    <row r="17" spans="8:8">
+    <row r="17" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H17" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="18" spans="8:8">
+    <row r="18" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H18" t="s">
         <v>104</v>
       </c>
@@ -2647,16 +2756,16 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D3A9745-558A-479E-B1B2-9C6EC5EEDA6F}">
   <dimension ref="B2:J28"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="20.26953125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.90625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="17.453125" customWidth="1"/>
-    <col min="8" max="8" width="23.81640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="25.6328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.21875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.44140625" customWidth="1"/>
+    <col min="8" max="8" width="23.88671875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="25.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:10">
+    <row r="2" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B2" s="1" t="s">
         <v>66</v>
       </c>
@@ -2673,7 +2782,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="3" spans="2:10">
+    <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>1</v>
       </c>
@@ -2690,7 +2799,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="2:10">
+    <row r="4" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
         <v>16</v>
       </c>
@@ -2707,7 +2816,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="5" spans="2:10">
+    <row r="5" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
         <v>74</v>
       </c>
@@ -2721,7 +2830,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="2:10">
+    <row r="6" spans="2:10" ht="15" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
         <v>109</v>
       </c>
@@ -2735,7 +2844,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="7" spans="2:10">
+    <row r="7" spans="2:10" ht="15" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
         <v>110</v>
       </c>
@@ -2752,7 +2861,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="8" spans="2:10">
+    <row r="8" spans="2:10" ht="15" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
         <v>92</v>
       </c>
@@ -2769,7 +2878,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="2:10">
+    <row r="9" spans="2:10" ht="15" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
         <v>75</v>
       </c>
@@ -2786,7 +2895,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="10" spans="2:10">
+    <row r="10" spans="2:10" ht="15" x14ac:dyDescent="0.3">
       <c r="D10" t="s">
         <v>116</v>
       </c>
@@ -2797,7 +2906,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="11" spans="2:10">
+    <row r="11" spans="2:10" ht="15" x14ac:dyDescent="0.3">
       <c r="D11" t="s">
         <v>117</v>
       </c>
@@ -2811,7 +2920,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="12" spans="2:10">
+    <row r="12" spans="2:10" ht="15" x14ac:dyDescent="0.3">
       <c r="D12" t="s">
         <v>119</v>
       </c>
@@ -2822,7 +2931,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="13" spans="2:10">
+    <row r="13" spans="2:10" ht="15" x14ac:dyDescent="0.3">
       <c r="D13" t="s">
         <v>140</v>
       </c>
@@ -2833,7 +2942,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="14" spans="2:10">
+    <row r="14" spans="2:10" x14ac:dyDescent="0.3">
       <c r="D14" t="s">
         <v>118</v>
       </c>
@@ -2844,17 +2953,17 @@
         <v>126</v>
       </c>
     </row>
-    <row r="15" spans="2:10">
+    <row r="15" spans="2:10" x14ac:dyDescent="0.3">
       <c r="D15" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="16" spans="2:10">
+    <row r="16" spans="2:10" x14ac:dyDescent="0.3">
       <c r="D16" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="18" spans="2:6">
+    <row r="18" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B18" s="1" t="s">
         <v>146</v>
       </c>
@@ -2865,7 +2974,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="19" spans="2:6">
+    <row r="19" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B19" t="s">
         <v>1</v>
       </c>
@@ -2876,7 +2985,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="2:6">
+    <row r="20" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B20" t="s">
         <v>92</v>
       </c>
@@ -2887,7 +2996,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="21" spans="2:6">
+    <row r="21" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B21" t="s">
         <v>147</v>
       </c>
@@ -2895,7 +3004,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="22" spans="2:6">
+    <row r="22" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B22" t="s">
         <v>148</v>
       </c>
@@ -2903,7 +3012,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="23" spans="2:6">
+    <row r="23" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B23" t="s">
         <v>149</v>
       </c>
@@ -2911,7 +3020,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="24" spans="2:6">
+    <row r="24" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B24" t="s">
         <v>150</v>
       </c>
@@ -2919,7 +3028,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="25" spans="2:6">
+    <row r="25" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B25" t="s">
         <v>151</v>
       </c>
@@ -2927,7 +3036,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="26" spans="2:6">
+    <row r="26" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B26" t="s">
         <v>152</v>
       </c>
@@ -2935,7 +3044,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="27" spans="2:6">
+    <row r="27" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B27" t="s">
         <v>153</v>
       </c>
@@ -2943,7 +3052,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="28" spans="2:6">
+    <row r="28" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B28" t="s">
         <v>154</v>
       </c>
@@ -2956,16 +3065,16 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{852D4CF3-1038-42B3-A697-EC51612C14F3}">
   <dimension ref="B2:J18"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="19.90625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21.08984375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.453125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.90625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="20.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.44140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19.88671875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="20.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:10">
+    <row r="2" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B2" s="1" t="s">
         <v>111</v>
       </c>
@@ -2982,7 +3091,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="3" spans="2:10">
+    <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>1</v>
       </c>
@@ -2999,7 +3108,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="2:10">
+    <row r="4" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
         <v>106</v>
       </c>
@@ -3016,7 +3125,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="2:10">
+    <row r="5" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
         <v>112</v>
       </c>
@@ -3030,7 +3139,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="6" spans="2:10">
+    <row r="6" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
         <v>113</v>
       </c>
@@ -3044,7 +3153,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="7" spans="2:10">
+    <row r="7" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
         <v>114</v>
       </c>
@@ -3055,7 +3164,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="8" spans="2:10">
+    <row r="8" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
         <v>20</v>
       </c>
@@ -3072,7 +3181,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="9" spans="2:10">
+    <row r="9" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
         <v>115</v>
       </c>
@@ -3089,7 +3198,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="10" spans="2:10">
+    <row r="10" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
         <v>116</v>
       </c>
@@ -3106,7 +3215,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="11" spans="2:10">
+    <row r="11" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
         <v>117</v>
       </c>
@@ -3120,7 +3229,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="12" spans="2:10">
+    <row r="12" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
         <v>119</v>
       </c>
@@ -3131,12 +3240,12 @@
         <v>130</v>
       </c>
     </row>
-    <row r="13" spans="2:10">
+    <row r="13" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="14" spans="2:10">
+    <row r="14" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
         <v>118</v>
       </c>
@@ -3144,7 +3253,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="15" spans="2:10">
+    <row r="15" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
         <v>142</v>
       </c>
@@ -3152,17 +3261,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="2:10">
+    <row r="16" spans="2:10" x14ac:dyDescent="0.3">
       <c r="D16" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="17" spans="4:4">
+    <row r="17" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D17" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="18" spans="4:4">
+    <row r="18" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D18" t="s">
         <v>162</v>
       </c>
@@ -3175,15 +3284,15 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{580FB0E5-89D5-4955-8D17-6E97D145D9F7}">
   <dimension ref="B2:H16"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="19.90625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="23.36328125" customWidth="1"/>
-    <col min="6" max="6" width="19.90625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.33203125" customWidth="1"/>
+    <col min="6" max="6" width="19.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8">
+    <row r="2" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B2" s="1" t="s">
         <v>111</v>
       </c>
@@ -3197,7 +3306,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="3" spans="2:8">
+    <row r="3" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>1</v>
       </c>
@@ -3211,7 +3320,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="2:8">
+    <row r="4" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
         <v>106</v>
       </c>
@@ -3225,7 +3334,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="5" spans="2:8">
+    <row r="5" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
         <v>112</v>
       </c>
@@ -3236,7 +3345,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="6" spans="2:8">
+    <row r="6" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
         <v>113</v>
       </c>
@@ -3247,7 +3356,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="7" spans="2:8">
+    <row r="7" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
         <v>114</v>
       </c>
@@ -3258,7 +3367,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="8" spans="2:8">
+    <row r="8" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
         <v>20</v>
       </c>
@@ -3269,7 +3378,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="2:8">
+    <row r="9" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
         <v>115</v>
       </c>
@@ -3283,7 +3392,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="10" spans="2:8">
+    <row r="10" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
         <v>116</v>
       </c>
@@ -3294,7 +3403,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="11" spans="2:8">
+    <row r="11" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
         <v>117</v>
       </c>
@@ -3305,7 +3414,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="12" spans="2:8">
+    <row r="12" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
         <v>119</v>
       </c>
@@ -3319,7 +3428,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="13" spans="2:8">
+    <row r="13" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
         <v>140</v>
       </c>
@@ -3333,7 +3442,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="2:8">
+    <row r="14" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
         <v>118</v>
       </c>
@@ -3344,7 +3453,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="15" spans="2:8">
+    <row r="15" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
         <v>142</v>
       </c>
@@ -3355,7 +3464,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="16" spans="2:8">
+    <row r="16" spans="2:8" x14ac:dyDescent="0.3">
       <c r="F16" s="1"/>
       <c r="H16" t="s">
         <v>176</v>
@@ -3369,13 +3478,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{543B08D0-87A8-44D6-9F83-94933D8C9C17}">
   <dimension ref="B2:D11"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="24.1796875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.26953125" customWidth="1"/>
+    <col min="2" max="2" width="24.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:4">
+    <row r="2" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B2" s="1" t="s">
         <v>105</v>
       </c>
@@ -3383,7 +3492,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="3" spans="2:4">
+    <row r="3" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>1</v>
       </c>
@@ -3391,7 +3500,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="2:4">
+    <row r="4" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
         <v>106</v>
       </c>
@@ -3399,7 +3508,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="5" spans="2:4">
+    <row r="5" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
         <v>142</v>
       </c>
@@ -3407,7 +3516,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="6" spans="2:4">
+    <row r="6" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
         <v>107</v>
       </c>
@@ -3415,7 +3524,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="7" spans="2:4">
+    <row r="7" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
         <v>180</v>
       </c>
@@ -3423,22 +3532,22 @@
         <v>172</v>
       </c>
     </row>
-    <row r="8" spans="2:4">
+    <row r="8" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="9" spans="2:4">
+    <row r="9" spans="2:4" x14ac:dyDescent="0.3">
       <c r="D9" s="1" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="10" spans="2:4">
+    <row r="10" spans="2:4" x14ac:dyDescent="0.3">
       <c r="D10" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="2:4">
+    <row r="11" spans="2:4" x14ac:dyDescent="0.3">
       <c r="D11" t="s">
         <v>182</v>
       </c>
@@ -3451,18 +3560,18 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D794D288-BDD7-47B9-8549-02ED03290623}">
   <dimension ref="B2:M25"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="18.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.44140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="17" customWidth="1"/>
     <col min="6" max="6" width="15" customWidth="1"/>
-    <col min="8" max="8" width="15.6328125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="19.90625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.7265625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="19.90625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="19.88671875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.77734375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="19.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:13">
+    <row r="2" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B2" s="1" t="s">
         <v>53</v>
       </c>
@@ -3485,7 +3594,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="3" spans="2:13">
+    <row r="3" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>1</v>
       </c>
@@ -3508,7 +3617,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="2:13">
+    <row r="4" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
         <v>217</v>
       </c>
@@ -3531,7 +3640,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="5" spans="2:13">
+    <row r="5" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
         <v>216</v>
       </c>
@@ -3554,7 +3663,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="6" spans="2:13">
+    <row r="6" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
         <v>218</v>
       </c>
@@ -3577,7 +3686,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="7" spans="2:13">
+    <row r="7" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
         <v>3</v>
       </c>
@@ -3600,7 +3709,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="8" spans="2:13">
+    <row r="8" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
         <v>192</v>
       </c>
@@ -3623,7 +3732,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="9" spans="2:13">
+    <row r="9" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
         <v>220</v>
       </c>
@@ -3646,7 +3755,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="10" spans="2:13">
+    <row r="10" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
         <v>219</v>
       </c>
@@ -3660,7 +3769,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="11" spans="2:13">
+    <row r="11" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
         <v>191</v>
       </c>
@@ -3674,7 +3783,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="12" spans="2:13">
+    <row r="12" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
         <v>225</v>
       </c>
@@ -3688,7 +3797,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="13" spans="2:13">
+    <row r="13" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
         <v>193</v>
       </c>
@@ -3702,22 +3811,22 @@
         <v>208</v>
       </c>
     </row>
-    <row r="14" spans="2:13">
+    <row r="14" spans="2:13" x14ac:dyDescent="0.3">
       <c r="J14" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="15" spans="2:13">
+    <row r="15" spans="2:13" x14ac:dyDescent="0.3">
       <c r="J15" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="17" spans="2:4">
+    <row r="17" spans="2:4" x14ac:dyDescent="0.3">
       <c r="D17" s="1" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="18" spans="2:4">
+    <row r="18" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B18" s="1" t="s">
         <v>185</v>
       </c>
@@ -3725,7 +3834,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="2:4">
+    <row r="19" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B19" t="s">
         <v>1</v>
       </c>
@@ -3733,7 +3842,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="20" spans="2:4">
+    <row r="20" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B20" t="s">
         <v>194</v>
       </c>
@@ -3741,7 +3850,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="21" spans="2:4">
+    <row r="21" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B21" t="s">
         <v>69</v>
       </c>
@@ -3749,22 +3858,22 @@
         <v>198</v>
       </c>
     </row>
-    <row r="22" spans="2:4">
+    <row r="22" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B22" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="23" spans="2:4">
+    <row r="23" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B23" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="24" spans="2:4">
+    <row r="24" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B24" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="25" spans="2:4">
+    <row r="25" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B25" t="s">
         <v>205</v>
       </c>
@@ -3777,17 +3886,17 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F800367-D121-468C-B2BA-C9E3C3CB19BA}">
   <dimension ref="B2:L8"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="12.54296875" customWidth="1"/>
-    <col min="4" max="4" width="10.6328125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.453125" customWidth="1"/>
-    <col min="8" max="8" width="20.08984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.44140625" customWidth="1"/>
+    <col min="4" max="4" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.44140625" customWidth="1"/>
+    <col min="8" max="8" width="20.109375" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="12" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="17.54296875" customWidth="1"/>
+    <col min="12" max="12" width="17.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:12">
+    <row r="2" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B2" s="1" t="s">
         <v>4</v>
       </c>
@@ -3807,7 +3916,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="3" spans="2:12">
+    <row r="3" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>1</v>
       </c>
@@ -3827,7 +3936,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="2:12">
+    <row r="4" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
         <v>5</v>
       </c>
@@ -3847,7 +3956,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="5" spans="2:12">
+    <row r="5" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
         <v>6</v>
       </c>
@@ -3864,17 +3973,17 @@
         <v>238</v>
       </c>
     </row>
-    <row r="6" spans="2:12">
+    <row r="6" spans="2:12" x14ac:dyDescent="0.3">
       <c r="L6" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="7" spans="2:12">
+    <row r="7" spans="2:12" x14ac:dyDescent="0.3">
       <c r="L7" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="8" spans="2:12">
+    <row r="8" spans="2:12" x14ac:dyDescent="0.3">
       <c r="L8" t="s">
         <v>241</v>
       </c>

--- a/Documents/DBdesign.xlsx
+++ b/Documents/DBdesign.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Gitlab\joboffer\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitLab\joboffer\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8909E14-0854-40A6-A01B-BE86E746EE8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{EC866685-AF1E-4348-AED4-D9D6F45DAE80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2856" yWindow="2964" windowWidth="23040" windowHeight="12168" firstSheet="3" activeTab="9" xr2:uid="{BEC21941-B947-480A-A7E6-7B63159DE119}"/>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="8" xr2:uid="{BEC21941-B947-480A-A7E6-7B63159DE119}"/>
   </bookViews>
   <sheets>
     <sheet name="RBAC+ABAC" sheetId="1" r:id="rId1"/>
@@ -25,6 +25,7 @@
     <sheet name="Comp&amp;Ben" sheetId="11" r:id="rId10"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -1011,7 +1012,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1496,16 +1497,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9EF47D5C-035D-491F-B6E5-626F15CDCBDA}">
   <dimension ref="B2:J51"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="16.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.88671875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.44140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.453125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.90625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.08984375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19.453125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16.6328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:10">
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1522,7 +1523,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="3" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:10">
       <c r="B3" t="s">
         <v>1</v>
       </c>
@@ -1539,7 +1540,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:10">
       <c r="B4" t="s">
         <v>47</v>
       </c>
@@ -1556,7 +1557,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:10">
       <c r="B5" t="s">
         <v>2</v>
       </c>
@@ -1573,7 +1574,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="6" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:10">
       <c r="B6" t="s">
         <v>3</v>
       </c>
@@ -1587,7 +1588,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:10">
       <c r="B9" s="1" t="s">
         <v>4</v>
       </c>
@@ -1598,7 +1599,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:10">
       <c r="B10" t="s">
         <v>1</v>
       </c>
@@ -1609,7 +1610,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:10">
       <c r="B11" t="s">
         <v>5</v>
       </c>
@@ -1620,7 +1621,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="12" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:10">
       <c r="B12" t="s">
         <v>6</v>
       </c>
@@ -1631,7 +1632,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:10">
       <c r="D13" t="s">
         <v>10</v>
       </c>
@@ -1639,32 +1640,32 @@
         <v>17</v>
       </c>
     </row>
-    <row r="14" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:10">
       <c r="F14" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="15" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:10">
       <c r="F15" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="16" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:10">
       <c r="F16" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:6">
       <c r="F17" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:6">
       <c r="F18" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:6">
       <c r="B21" s="1" t="s">
         <v>22</v>
       </c>
@@ -1675,7 +1676,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:6">
       <c r="B22" t="s">
         <v>1</v>
       </c>
@@ -1686,7 +1687,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:6">
       <c r="B23" t="s">
         <v>23</v>
       </c>
@@ -1697,7 +1698,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:6">
       <c r="B24" t="s">
         <v>24</v>
       </c>
@@ -1708,107 +1709,107 @@
         <v>26</v>
       </c>
     </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:6">
       <c r="F25" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:6">
       <c r="F26" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:6">
       <c r="F27" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:6">
       <c r="B30" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="31" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:6">
       <c r="B31" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:6">
       <c r="B32" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="33" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:2">
       <c r="B33" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="34" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:2">
       <c r="B34" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="37" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:2">
       <c r="B37" s="1" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="38" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:2">
       <c r="B38" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:2">
       <c r="B39" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="40" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:2">
       <c r="B40" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="41" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:2">
       <c r="B41" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="42" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:2">
       <c r="B42" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="43" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:2">
       <c r="B43" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="44" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:2">
       <c r="B44" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="45" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:2">
       <c r="B45" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="48" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:2">
       <c r="B48" s="1" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="49" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:2">
       <c r="B49" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:2">
       <c r="B50" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="51" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:2">
       <c r="B51" t="s">
         <v>50</v>
       </c>
@@ -1821,23 +1822,23 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54F2E5B3-A5D7-48E1-BBB6-A4B5E81A5574}">
   <dimension ref="B1:R35"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="16.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.109375" customWidth="1"/>
-    <col min="6" max="6" width="19.44140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.6640625" customWidth="1"/>
-    <col min="10" max="10" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.6328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.08984375" customWidth="1"/>
+    <col min="6" max="6" width="19.453125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.6328125" customWidth="1"/>
+    <col min="10" max="10" width="14.36328125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="16" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15.21875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.1796875" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="16" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.08984375" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="16" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="15.21875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="15.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="2" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="2:18" ht="15" thickBot="1"/>
+    <row r="2" spans="2:18" ht="15" thickBot="1">
       <c r="B2" s="1" t="s">
         <v>254</v>
       </c>
@@ -1863,7 +1864,7 @@
       </c>
       <c r="R2" s="9"/>
     </row>
-    <row r="3" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:18" ht="15" thickBot="1">
       <c r="B3" t="s">
         <v>1</v>
       </c>
@@ -1895,7 +1896,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="4" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:18" ht="15" thickBot="1">
       <c r="B4" t="s">
         <v>242</v>
       </c>
@@ -1927,7 +1928,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="5" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:18" ht="15" thickBot="1">
       <c r="B5" t="s">
         <v>125</v>
       </c>
@@ -1953,7 +1954,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="6" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:18" ht="15" thickBot="1">
       <c r="B6" t="s">
         <v>310</v>
       </c>
@@ -1979,7 +1980,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="7" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:18" ht="15" thickBot="1">
       <c r="B7" t="s">
         <v>244</v>
       </c>
@@ -2008,7 +2009,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="8" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:18" ht="15" thickBot="1">
       <c r="B8" t="s">
         <v>266</v>
       </c>
@@ -2034,7 +2035,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="9" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:18" ht="15" thickBot="1">
       <c r="B9" t="s">
         <v>246</v>
       </c>
@@ -2060,7 +2061,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="10" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:18" ht="15" thickBot="1">
       <c r="B10" t="s">
         <v>247</v>
       </c>
@@ -2086,7 +2087,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="11" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:18" ht="15" thickBot="1">
       <c r="B11" t="s">
         <v>249</v>
       </c>
@@ -2112,7 +2113,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="12" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:18" ht="15" thickBot="1">
       <c r="B12" t="s">
         <v>248</v>
       </c>
@@ -2141,7 +2142,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="13" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:18" ht="15" thickBot="1">
       <c r="B13" t="s">
         <v>250</v>
       </c>
@@ -2170,7 +2171,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="14" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:18" ht="15" thickBot="1">
       <c r="B14" t="s">
         <v>204</v>
       </c>
@@ -2199,7 +2200,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="15" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:18" ht="15" thickBot="1">
       <c r="B15" t="s">
         <v>251</v>
       </c>
@@ -2225,7 +2226,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="16" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:18" ht="15" thickBot="1">
       <c r="B16" t="s">
         <v>307</v>
       </c>
@@ -2251,12 +2252,12 @@
         <v>304</v>
       </c>
     </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:6">
       <c r="D17" s="1" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:6">
       <c r="D18" t="s">
         <v>1</v>
       </c>
@@ -2264,7 +2265,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:6">
       <c r="D19" t="s">
         <v>245</v>
       </c>
@@ -2272,7 +2273,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:6">
       <c r="B20" s="1" t="s">
         <v>313</v>
       </c>
@@ -2280,7 +2281,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:6">
       <c r="B21" t="s">
         <v>1</v>
       </c>
@@ -2288,7 +2289,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:6">
       <c r="B22" t="s">
         <v>311</v>
       </c>
@@ -2296,7 +2297,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="23" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:6">
       <c r="B23" t="s">
         <v>312</v>
       </c>
@@ -2304,7 +2305,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:6">
       <c r="B24" t="s">
         <v>125</v>
       </c>
@@ -2315,7 +2316,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:6">
       <c r="B25" t="s">
         <v>310</v>
       </c>
@@ -2323,7 +2324,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:6">
       <c r="B26" t="s">
         <v>244</v>
       </c>
@@ -2334,7 +2335,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:6">
       <c r="B27" t="s">
         <v>266</v>
       </c>
@@ -2345,7 +2346,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:6">
       <c r="B28" t="s">
         <v>246</v>
       </c>
@@ -2353,17 +2354,17 @@
         <v>259</v>
       </c>
     </row>
-    <row r="29" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:6">
       <c r="B29" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:6">
       <c r="B30" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="31" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:6">
       <c r="B31" t="s">
         <v>248</v>
       </c>
@@ -2371,7 +2372,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="32" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:6">
       <c r="B32" t="s">
         <v>250</v>
       </c>
@@ -2379,7 +2380,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:4">
       <c r="B33" t="s">
         <v>204</v>
       </c>
@@ -2387,12 +2388,12 @@
         <v>309</v>
       </c>
     </row>
-    <row r="34" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:4">
       <c r="B34" t="s">
         <v>251</v>
       </c>
     </row>
-    <row r="35" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:4">
       <c r="B35" t="s">
         <v>307</v>
       </c>
@@ -2411,14 +2412,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{026B99F0-FC57-47AB-AF03-F4ABCCD02BF2}">
   <dimension ref="B2:H16"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="22.44140625" customWidth="1"/>
-    <col min="4" max="4" width="24.44140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.453125" customWidth="1"/>
+    <col min="4" max="4" width="24.453125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:8">
       <c r="B2" s="1" t="s">
         <v>53</v>
       </c>
@@ -2432,7 +2433,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:8">
       <c r="B3" t="s">
         <v>1</v>
       </c>
@@ -2446,7 +2447,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:8">
       <c r="B4" t="s">
         <v>54</v>
       </c>
@@ -2460,7 +2461,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:8">
       <c r="B5" t="s">
         <v>55</v>
       </c>
@@ -2471,7 +2472,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="6" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:8">
       <c r="B6" t="s">
         <v>56</v>
       </c>
@@ -2482,7 +2483,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:8">
       <c r="B7" t="s">
         <v>3</v>
       </c>
@@ -2493,7 +2494,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:8">
       <c r="B8" t="s">
         <v>57</v>
       </c>
@@ -2504,7 +2505,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="9" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:8">
       <c r="B9" t="s">
         <v>58</v>
       </c>
@@ -2515,7 +2516,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:8">
       <c r="B10" t="s">
         <v>59</v>
       </c>
@@ -2526,7 +2527,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="11" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:8">
       <c r="B11" t="s">
         <v>60</v>
       </c>
@@ -2537,7 +2538,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="12" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:8">
       <c r="B12" t="s">
         <v>61</v>
       </c>
@@ -2545,22 +2546,22 @@
         <v>73</v>
       </c>
     </row>
-    <row r="13" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:8">
       <c r="B13" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="14" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:8">
       <c r="B14" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="15" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:8">
       <c r="B15" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="16" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:8">
       <c r="B16" t="s">
         <v>64</v>
       </c>
@@ -2573,16 +2574,16 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9AD6FEA5-0945-4178-A2F8-A72772503D4A}">
   <dimension ref="B2:J18"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="23.77734375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.81640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.08984375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="14" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="19.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.6328125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="19.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:10">
       <c r="B2" s="1" t="s">
         <v>66</v>
       </c>
@@ -2599,7 +2600,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="3" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:10">
       <c r="B3" t="s">
         <v>1</v>
       </c>
@@ -2616,7 +2617,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:10">
       <c r="B4" t="s">
         <v>16</v>
       </c>
@@ -2633,7 +2634,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:10">
       <c r="B5" t="s">
         <v>74</v>
       </c>
@@ -2650,7 +2651,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="6" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:10">
       <c r="B6" t="s">
         <v>109</v>
       </c>
@@ -2664,7 +2665,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:10">
       <c r="B7" t="s">
         <v>110</v>
       </c>
@@ -2672,7 +2673,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="8" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:10">
       <c r="B8" t="s">
         <v>92</v>
       </c>
@@ -2680,7 +2681,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:10">
       <c r="B9" t="s">
         <v>75</v>
       </c>
@@ -2688,7 +2689,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="10" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:10">
       <c r="B10" t="s">
         <v>89</v>
       </c>
@@ -2696,7 +2697,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:10">
       <c r="B11" t="s">
         <v>90</v>
       </c>
@@ -2704,17 +2705,17 @@
         <v>100</v>
       </c>
     </row>
-    <row r="12" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:10">
       <c r="H12" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="13" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:10">
       <c r="H13" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="14" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:10">
       <c r="B14" s="1" t="s">
         <v>184</v>
       </c>
@@ -2722,7 +2723,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="15" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:10">
       <c r="B15" t="s">
         <v>1</v>
       </c>
@@ -2730,7 +2731,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="16" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:10">
       <c r="B16" t="s">
         <v>156</v>
       </c>
@@ -2738,12 +2739,12 @@
         <v>89</v>
       </c>
     </row>
-    <row r="17" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="17" spans="8:8">
       <c r="H17" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="18" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="18" spans="8:8">
       <c r="H18" t="s">
         <v>104</v>
       </c>
@@ -2756,16 +2757,16 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D3A9745-558A-479E-B1B2-9C6EC5EEDA6F}">
   <dimension ref="B2:J28"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="20.21875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.88671875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="17.44140625" customWidth="1"/>
-    <col min="8" max="8" width="23.88671875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="25.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.1796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.90625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.453125" customWidth="1"/>
+    <col min="8" max="8" width="23.90625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="25.6328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:10">
       <c r="B2" s="1" t="s">
         <v>66</v>
       </c>
@@ -2782,7 +2783,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="3" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:10">
       <c r="B3" t="s">
         <v>1</v>
       </c>
@@ -2799,7 +2800,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:10">
       <c r="B4" t="s">
         <v>16</v>
       </c>
@@ -2816,7 +2817,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:10">
       <c r="B5" t="s">
         <v>74</v>
       </c>
@@ -2830,7 +2831,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="2:10" ht="15" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:10">
       <c r="B6" t="s">
         <v>109</v>
       </c>
@@ -2844,7 +2845,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="7" spans="2:10" ht="15" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:10">
       <c r="B7" t="s">
         <v>110</v>
       </c>
@@ -2861,7 +2862,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="8" spans="2:10" ht="15" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:10">
       <c r="B8" t="s">
         <v>92</v>
       </c>
@@ -2878,7 +2879,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="2:10" ht="15" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:10">
       <c r="B9" t="s">
         <v>75</v>
       </c>
@@ -2895,7 +2896,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="10" spans="2:10" ht="15" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:10">
       <c r="D10" t="s">
         <v>116</v>
       </c>
@@ -2906,7 +2907,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="11" spans="2:10" ht="15" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:10">
       <c r="D11" t="s">
         <v>117</v>
       </c>
@@ -2920,7 +2921,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="12" spans="2:10" ht="15" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:10">
       <c r="D12" t="s">
         <v>119</v>
       </c>
@@ -2931,7 +2932,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="13" spans="2:10" ht="15" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:10">
       <c r="D13" t="s">
         <v>140</v>
       </c>
@@ -2942,7 +2943,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="14" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:10">
       <c r="D14" t="s">
         <v>118</v>
       </c>
@@ -2953,17 +2954,17 @@
         <v>126</v>
       </c>
     </row>
-    <row r="15" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:10">
       <c r="D15" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="16" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:10">
       <c r="D16" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:6">
       <c r="B18" s="1" t="s">
         <v>146</v>
       </c>
@@ -2974,7 +2975,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:6">
       <c r="B19" t="s">
         <v>1</v>
       </c>
@@ -2985,7 +2986,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:6">
       <c r="B20" t="s">
         <v>92</v>
       </c>
@@ -2996,7 +2997,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:6">
       <c r="B21" t="s">
         <v>147</v>
       </c>
@@ -3004,7 +3005,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:6">
       <c r="B22" t="s">
         <v>148</v>
       </c>
@@ -3012,7 +3013,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="23" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:6">
       <c r="B23" t="s">
         <v>149</v>
       </c>
@@ -3020,7 +3021,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:6">
       <c r="B24" t="s">
         <v>150</v>
       </c>
@@ -3028,7 +3029,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:6">
       <c r="B25" t="s">
         <v>151</v>
       </c>
@@ -3036,7 +3037,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="26" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:6">
       <c r="B26" t="s">
         <v>152</v>
       </c>
@@ -3044,7 +3045,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:6">
       <c r="B27" t="s">
         <v>153</v>
       </c>
@@ -3052,7 +3053,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:6">
       <c r="B28" t="s">
         <v>154</v>
       </c>
@@ -3065,16 +3066,16 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{852D4CF3-1038-42B3-A697-EC51612C14F3}">
   <dimension ref="B2:J18"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="19.88671875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21.109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.44140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.88671875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="20.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.90625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.08984375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.453125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19.90625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="20.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:10">
       <c r="B2" s="1" t="s">
         <v>111</v>
       </c>
@@ -3091,7 +3092,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="3" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:10">
       <c r="B3" t="s">
         <v>1</v>
       </c>
@@ -3108,7 +3109,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:10">
       <c r="B4" t="s">
         <v>106</v>
       </c>
@@ -3125,7 +3126,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:10">
       <c r="B5" t="s">
         <v>112</v>
       </c>
@@ -3139,7 +3140,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="6" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:10">
       <c r="B6" t="s">
         <v>113</v>
       </c>
@@ -3153,7 +3154,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:10">
       <c r="B7" t="s">
         <v>114</v>
       </c>
@@ -3164,7 +3165,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="8" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:10">
       <c r="B8" t="s">
         <v>20</v>
       </c>
@@ -3181,7 +3182,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:10">
       <c r="B9" t="s">
         <v>115</v>
       </c>
@@ -3198,7 +3199,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="10" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:10">
       <c r="B10" t="s">
         <v>116</v>
       </c>
@@ -3215,7 +3216,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:10">
       <c r="B11" t="s">
         <v>117</v>
       </c>
@@ -3229,7 +3230,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="12" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:10">
       <c r="B12" t="s">
         <v>119</v>
       </c>
@@ -3240,12 +3241,12 @@
         <v>130</v>
       </c>
     </row>
-    <row r="13" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:10">
       <c r="B13" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="14" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:10">
       <c r="B14" t="s">
         <v>118</v>
       </c>
@@ -3253,7 +3254,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="15" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:10">
       <c r="B15" t="s">
         <v>142</v>
       </c>
@@ -3261,17 +3262,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:10">
       <c r="D16" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="17" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="4:4">
       <c r="D17" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="18" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="4:4">
       <c r="D18" t="s">
         <v>162</v>
       </c>
@@ -3284,15 +3285,15 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{580FB0E5-89D5-4955-8D17-6E97D145D9F7}">
   <dimension ref="B2:H16"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="19.88671875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="23.33203125" customWidth="1"/>
-    <col min="6" max="6" width="19.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.90625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.36328125" customWidth="1"/>
+    <col min="6" max="6" width="19.90625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:8">
       <c r="B2" s="1" t="s">
         <v>111</v>
       </c>
@@ -3306,7 +3307,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:8">
       <c r="B3" t="s">
         <v>1</v>
       </c>
@@ -3320,7 +3321,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:8">
       <c r="B4" t="s">
         <v>106</v>
       </c>
@@ -3334,7 +3335,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:8">
       <c r="B5" t="s">
         <v>112</v>
       </c>
@@ -3345,7 +3346,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="6" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:8">
       <c r="B6" t="s">
         <v>113</v>
       </c>
@@ -3356,7 +3357,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:8">
       <c r="B7" t="s">
         <v>114</v>
       </c>
@@ -3367,7 +3368,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:8">
       <c r="B8" t="s">
         <v>20</v>
       </c>
@@ -3378,7 +3379,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:8">
       <c r="B9" t="s">
         <v>115</v>
       </c>
@@ -3392,7 +3393,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:8">
       <c r="B10" t="s">
         <v>116</v>
       </c>
@@ -3403,7 +3404,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="11" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:8">
       <c r="B11" t="s">
         <v>117</v>
       </c>
@@ -3414,7 +3415,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="12" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:8">
       <c r="B12" t="s">
         <v>119</v>
       </c>
@@ -3428,7 +3429,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="13" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:8">
       <c r="B13" t="s">
         <v>140</v>
       </c>
@@ -3442,7 +3443,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:8">
       <c r="B14" t="s">
         <v>118</v>
       </c>
@@ -3453,7 +3454,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="15" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:8">
       <c r="B15" t="s">
         <v>142</v>
       </c>
@@ -3464,7 +3465,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="16" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:8">
       <c r="F16" s="1"/>
       <c r="H16" t="s">
         <v>176</v>
@@ -3478,13 +3479,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{543B08D0-87A8-44D6-9F83-94933D8C9C17}">
   <dimension ref="B2:D11"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="24.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.21875" customWidth="1"/>
+    <col min="2" max="2" width="24.08984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:4">
       <c r="B2" s="1" t="s">
         <v>105</v>
       </c>
@@ -3492,7 +3493,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="3" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:4">
       <c r="B3" t="s">
         <v>1</v>
       </c>
@@ -3500,7 +3501,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:4">
       <c r="B4" t="s">
         <v>106</v>
       </c>
@@ -3508,7 +3509,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="5" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:4">
       <c r="B5" t="s">
         <v>142</v>
       </c>
@@ -3516,7 +3517,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="6" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:4">
       <c r="B6" t="s">
         <v>107</v>
       </c>
@@ -3524,7 +3525,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="7" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:4">
       <c r="B7" t="s">
         <v>180</v>
       </c>
@@ -3532,22 +3533,22 @@
         <v>172</v>
       </c>
     </row>
-    <row r="8" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:4">
       <c r="B8" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="9" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:4">
       <c r="D9" s="1" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="10" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:4">
       <c r="D10" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:4">
       <c r="D11" t="s">
         <v>182</v>
       </c>
@@ -3560,18 +3561,18 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D794D288-BDD7-47B9-8549-02ED03290623}">
   <dimension ref="B2:M25"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.453125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="17" customWidth="1"/>
     <col min="6" max="6" width="15" customWidth="1"/>
-    <col min="8" max="8" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="19.88671875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.77734375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="19.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.6328125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="19.90625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.81640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="19.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:13">
       <c r="B2" s="1" t="s">
         <v>53</v>
       </c>
@@ -3594,7 +3595,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="3" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:13">
       <c r="B3" t="s">
         <v>1</v>
       </c>
@@ -3617,7 +3618,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:13">
       <c r="B4" t="s">
         <v>217</v>
       </c>
@@ -3640,7 +3641,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="5" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:13">
       <c r="B5" t="s">
         <v>216</v>
       </c>
@@ -3663,7 +3664,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="6" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:13">
       <c r="B6" t="s">
         <v>218</v>
       </c>
@@ -3686,7 +3687,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="7" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:13">
       <c r="B7" t="s">
         <v>3</v>
       </c>
@@ -3709,7 +3710,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="8" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:13">
       <c r="B8" t="s">
         <v>192</v>
       </c>
@@ -3732,7 +3733,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="9" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:13">
       <c r="B9" t="s">
         <v>220</v>
       </c>
@@ -3755,7 +3756,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="10" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:13">
       <c r="B10" t="s">
         <v>219</v>
       </c>
@@ -3769,7 +3770,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="11" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:13">
       <c r="B11" t="s">
         <v>191</v>
       </c>
@@ -3783,7 +3784,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="12" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:13">
       <c r="B12" t="s">
         <v>225</v>
       </c>
@@ -3797,7 +3798,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="13" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:13">
       <c r="B13" t="s">
         <v>193</v>
       </c>
@@ -3811,22 +3812,22 @@
         <v>208</v>
       </c>
     </row>
-    <row r="14" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:13">
       <c r="J14" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="15" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:13">
       <c r="J15" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:4">
       <c r="D17" s="1" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:4">
       <c r="B18" s="1" t="s">
         <v>185</v>
       </c>
@@ -3834,7 +3835,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:4">
       <c r="B19" t="s">
         <v>1</v>
       </c>
@@ -3842,7 +3843,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:4">
       <c r="B20" t="s">
         <v>194</v>
       </c>
@@ -3850,7 +3851,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="21" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:4">
       <c r="B21" t="s">
         <v>69</v>
       </c>
@@ -3858,22 +3859,22 @@
         <v>198</v>
       </c>
     </row>
-    <row r="22" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:4">
       <c r="B22" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="23" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:4">
       <c r="B23" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="24" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:4">
       <c r="B24" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="25" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:4">
       <c r="B25" t="s">
         <v>205</v>
       </c>
@@ -3886,17 +3887,17 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F800367-D121-468C-B2BA-C9E3C3CB19BA}">
   <dimension ref="B2:L8"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="12.44140625" customWidth="1"/>
-    <col min="4" max="4" width="10.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.44140625" customWidth="1"/>
-    <col min="8" max="8" width="20.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.453125" customWidth="1"/>
+    <col min="4" max="4" width="10.6328125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.453125" customWidth="1"/>
+    <col min="8" max="8" width="20.08984375" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="12" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="17.44140625" customWidth="1"/>
+    <col min="12" max="12" width="17.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:12">
       <c r="B2" s="1" t="s">
         <v>4</v>
       </c>
@@ -3916,7 +3917,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="3" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:12">
       <c r="B3" t="s">
         <v>1</v>
       </c>
@@ -3936,7 +3937,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:12">
       <c r="B4" t="s">
         <v>5</v>
       </c>
@@ -3956,7 +3957,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:12">
       <c r="B5" t="s">
         <v>6</v>
       </c>
@@ -3973,17 +3974,17 @@
         <v>238</v>
       </c>
     </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:12">
       <c r="L6" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:12">
       <c r="L7" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:12">
       <c r="L8" t="s">
         <v>241</v>
       </c>
